--- a/deliverables/RFP-027/Qiddiya - TSE Irrigation Storage Tanks - Cost Assessment - Rev 02 - 30 Sep 2026.xlsx
+++ b/deliverables/RFP-027/Qiddiya - TSE Irrigation Storage Tanks - Cost Assessment - Rev 02 - 30 Sep 2026.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="1116">
   <si>
     <t xml:space="preserve">PROJECT INFORMATION</t>
   </si>
@@ -2286,7 +2286,7 @@
     <t xml:space="preserve">Testing and commissioning as programmed - both tanks in parallel (working days)</t>
   </si>
   <si>
-    <t xml:space="preserve">Activities QCD18TSECONTCT12050 and QCD18TSECONTCT22030, 09 to 16-Dec-2026, 7 working days each, in parallel. Not carried: the Engineer's (KEO) email of 30-Aug-2026 states that installation and testing will not be in parallel and that one tank is filled and the water re-used for the second. The sequential fit is at P18 to P21</t>
+    <t xml:space="preserve">Basis A only: activities QCD18TSECONTCT12050 and QCD18TSECONTCT22030, 09 to 16-Dec-2026, 7 working days each, in parallel, with two simultaneous fills. Not carried: the Engineer's (KEO) email of 30-Aug-2026 states that installation and testing will not be in parallel and that one tank is filled and the water re-used for the second. The sequential sequence carried on Basis B is at P18 to P22; the same sequence fitted to the submitted erection dates is the sensitivity S1 below</t>
   </si>
   <si>
     <t xml:space="preserve">P18</t>
@@ -2295,7 +2295,7 @@
     <t xml:space="preserve">Hydrostatic test - Tank 1, before the tie-in (working days)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fitted on both bases: starts the working day after the Tank 1 mechanical works and takes the 7 working days the Contractor programmed per tank. On the submitted dates it sits inside the 15 working days of float the programme gives Tank 1 (17 to 24-Nov-2026), so it does not delay anything. Assumptions: Tank 1 internals flushed and nozzles blind-flanged (RFP Scope of Works work packages 4 and 5); fill by tankered supply pending the Employer's confirmation of a local source; the water is retained in Tank 1 until Tank 2 is ready - losses are the 10 per cent top-up at 'Build-Up' line 7.5</t>
+    <t xml:space="preserve">Basis B: starts the working day after the Tank 1 mechanical works and takes the 7 working days the Contractor programmed per tank (the only programme evidence of a test duration). Assumptions: Tank 1 internals flushed and nozzles blind-flanged (RFP Scope of Works work packages 4 and 5); fill by tankered supply pending the Employer's confirmation of a local source; the water is retained in Tank 1 until Tank 2 is ready - losses are the 10 per cent top-up at 'Build-Up' line 7.5</t>
   </si>
   <si>
     <t xml:space="preserve">P19</t>
@@ -2313,7 +2313,7 @@
     <t xml:space="preserve">Hydrostatic test - Tank 2 (working days)</t>
   </si>
   <si>
-    <t xml:space="preserve">Follows the transfer; 7 working days as programmed per tank. On the submitted dates 08 to 15-Dec-2026, ending within the programmed testing window</t>
+    <t xml:space="preserve">Follows the transfer; 7 working days as programmed per tank</t>
   </si>
   <si>
     <t xml:space="preserve">P21</t>
@@ -2322,7 +2322,7 @@
     <t xml:space="preserve">Component and subsystem checks after the tie-in - instruments, nozzles, valves, ladders; tank-pump-network interfaces (working days)</t>
   </si>
   <si>
-    <t xml:space="preserve">RFP Scope of Works 5.2, component testing and subsystem validation. Follows the tie-in on both bases and may overlap the Tank 2 hydrostatic test, because these checks do not need both tanks in service. 3 working days is an assessed assumption: the Contractor's programme has no separate activity for this stage (its 7-working-day 'Testing &amp; Commissioning' activities cover the hydrostatic test and commissioning of each tank together), and programme durations are in any case not of themselves payable</t>
+    <t xml:space="preserve">RFP Scope of Works 5.2, component testing and subsystem validation. Follows the tie-in and may overlap the Tank 2 hydrostatic test, because these checks do not need both tanks in service. 3 working days is an assessed assumption, not a programme figure: the Contractor's programme has no separate activity for this stage - its two 7-working-day 'Testing &amp; Commissioning' activities cover the hydrostatic test and the commissioning of each tank together - so the sequential basis separates 7 working days per hydrostatic test (the programmed figure) from 3 plus 3 working days for the checks and the integrated commissioning (assessed). Programme durations are in any case not of themselves payable</t>
   </si>
   <si>
     <t xml:space="preserve">P21b</t>
@@ -2331,7 +2331,7 @@
     <t xml:space="preserve">Integrated system commissioning - full operational demonstration and witness testing (working days)</t>
   </si>
   <si>
-    <t xml:space="preserve">RFP Scope of Works 5.2, integrated system commissioning. Starts the working day after the last of the tie-in (P16), the Tank 2 hydrostatic test (P20) and the component checks (P21): both tanks must have passed and be connected before full operation is demonstrated. 3 working days is an assessed assumption on the same footing as P21. On the submitted erection dates the Tank 2 test ends 15-Dec-2026, so completion falls after the Contractor's programmed date of 16-Dec-2026; that is a consequence of testing sequentially, as the Engineer requires, and is shown, not forced either way</t>
+    <t xml:space="preserve">RFP Scope of Works 5.2, integrated system commissioning. Starts the working day after the last of the tie-in (P16), the Tank 2 hydrostatic test (P20) and the component checks (P21): both tanks must have passed and be connected before full operation is demonstrated. 3 working days is an assessed assumption on the same footing as P21</t>
   </si>
   <si>
     <t xml:space="preserve">P22</t>
@@ -2340,7 +2340,7 @@
     <t xml:space="preserve">Completion of testing and commissioning - both tanks</t>
   </si>
   <si>
-    <t xml:space="preserve">End of the integrated system commissioning. The Contractor's programme has completion milestones QCD18TSEOMS1040 and 1050 on 16-Dec-2026 with parallel testing</t>
+    <t xml:space="preserve">A: completion milestones QCD18TSEOMS1040 and 1050, 16-Dec-2026, with parallel testing. B: end of the integrated system commissioning, conditional on the Tank 1 test preceding the tie-in (P18); if it cannot, see sensitivity S2</t>
   </si>
   <si>
     <t xml:space="preserve">P23</t>
@@ -2349,7 +2349,7 @@
     <t xml:space="preserve">Demobilisation, as-built drawings and close-out documents (working days)</t>
   </si>
   <si>
-    <t xml:space="preserve">Activities QCD18TSEDMOB1020 and QCD18TSEDMOB3020, programmed 17 to 24-Dec-2026, 7 working days in parallel. On both bases re-timed to follow the completion of sequential testing (P22); the programme as submitted, with parallel testing, ends on 24-Dec-2026</t>
+    <t xml:space="preserve">Activities QCD18TSEDMOB1020 and QCD18TSEDMOB3020, 17 to 24-Dec-2026, 7 working days in parallel. B follows the completion of testing (P22)</t>
   </si>
   <si>
     <t xml:space="preserve">Derived periods used on the 'Build-Up' tab</t>
@@ -2361,7 +2361,7 @@
     <t xml:space="preserve">Site period - mobilisation start to demobilisation finish (calendar days)</t>
   </si>
   <si>
-    <t xml:space="preserve">Site staff, workforce transport, welfare cabins, WC, water tank and deliveries, the continuous 30 kVA welfare generator, the site pick-up and the watchman run for this period, which includes the demobilisation week so that supervision, HSE and welfare cover the demobilisation. On both bases the end is set by the external readiness milestone of 03-Dec-2026 and the tie-in, sequential testing, commissioning and demobilisation that follow it; the bases differ only in how the Tank 2 test sits against the tie-in. The programme as submitted, with parallel testing, gives 22-Aug to 24-Dec-2026, 125 days</t>
+    <t xml:space="preserve">Site staff, workforce transport, welfare cabins, WC, water tank and deliveries, the continuous 30 kVA welfare generator, the site pick-up and the watchman run for this period, which includes the demobilisation week so that supervision, HSE and welfare cover the demobilisation. A: the programme as submitted, 22-Aug to 24-Dec-2026. B: the end is set by the external readiness milestone of 03-Dec-2026 and the tie-in, sequential testing, commissioning and demobilisation that follow it, conditional on the early Tank 1 test (P18); the site engineer's 3 close-out days at 'Build-Up' line 1.22 fall after this period and are intentionally off-site visits, not a second allowance</t>
   </si>
   <si>
     <t xml:space="preserve">D2</t>
@@ -2418,6 +2418,36 @@
     <t xml:space="preserve">A: first delivery 08-Sep-2026 to Tank 2 roof finish 30-Nov-2026. B: efficient sequence; storage between staged deliveries is the Contractor's risk</t>
   </si>
   <si>
+    <t xml:space="preserve">Sensitivities - not carried; same durations and dependencies as P18 to P23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sequential testing on the submitted erection dates - Tank 1 test after its mechanical works, transfer after Tank 2 mechanical works, Tank 2 test, then integrated commissioning (calendar days from mobilisation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tank 1 test 17 to 24-Nov-2026 within its float; transfer 05 to 07-Dec after the Tank 2 mechanical works; Tank 2 test 08 to 15-Dec; integrated commissioning 16 to 19-Dec-2026, three working days after the Contractor's 16-Dec-2026 completion milestone. Shows that the Engineer's sequential requirement extends the submitted programme unless the Contractor re-sequences; not carried</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis B if the Tank 1 test cannot precede the tie-in - Tank 1 test after the tie-in, transfer, Tank 2 test, integrated commissioning, demobilisation (calendar days from mobilisation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tank 1 test 09 to 16-Dec-2026; transfer 17 to 20-Dec; Tank 2 test 21 to 28-Dec; component checks 09 to 12-Dec in parallel; integrated commissioning 29 to 31-Dec-2026; demobilisation 02 to 09-Jan-2027 (Fridays and the calendar exception excluded). The additional site days against D1 (Basis B) are shown at S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2 - effect on the carried assessment (additional calendar days; additional amount in SAR, excluding Overhead and Profit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional site days multiplied by the monthly rates of the lines priced on the site period D1 ('Build-Up' 1.1 to 1.8, 1.10, 1.12, 1.13, 5.8, 5.9) and on the works period D2 (5.7), with two extra water deliveries a week, months rounded as in Section 4. Not carried: it applies only if the Engineer does not accept the early Tank 1 test</t>
+  </si>
+  <si>
     <t xml:space="preserve">4. 'BUILD-UP' LINES WHOSE QUANTITY IS TAKEN FROM THIS TAB - BOTH BASES SIDE BY SIDE</t>
   </si>
   <si>
@@ -2508,13 +2538,13 @@
     <t xml:space="preserve">Top-up at 10 per cent of the water filled: of two fills on A, of one fill on B (retention in Tank 1 between P18 and P19)</t>
   </si>
   <si>
-    <t xml:space="preserve">Component checks P21 and integrated commissioning P21b, plus one day at each hydrostatic test hold; the fills and holds themselves are supervised by the QA/QC inspector (line 1.3) and the supplier's leak-test supervision within Item 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 No. technicians for the component checks P21 and the integrated commissioning P21b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tie-in P16 working days plus one day of integrated commissioning</t>
+    <t xml:space="preserve">A: the programmed 7-working-day parallel testing and commissioning activity plus one day at the hold. B: component checks P21 (3 days) and integrated commissioning P21b (3 days), both assessed assumptions, plus one day at each hydrostatic test hold; the fills and holds themselves are supervised by the QA/QC inspector (line 1.3) and the supplier's leak-test supervision within Item 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 No. technicians: A for the 7-day programmed activity; B for the component checks P21 and the integrated commissioning P21b (6 days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tie-in P16 working days plus one day of integrated commissioning, both bases</t>
   </si>
   <si>
     <t xml:space="preserve">Tanker and pump standby: 3 fill days and 1 hold day for Tank 1, 3 transfer days and 1 hold day for Tank 2; the same on both bases because the programme's parallel testing would need the same standby for two simultaneous fills</t>
@@ -3883,7 +3913,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4117,6 +4147,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5683,7 +5717,7 @@
         <v>96</v>
       </c>
       <c r="D9" s="18" t="n">
-        <f aca="false">Programme!$G$56</f>
+        <f aca="false">Programme!$G$60</f>
         <v>4.1</v>
       </c>
       <c r="E9" s="18" t="n">
@@ -5708,7 +5742,7 @@
         <v>96</v>
       </c>
       <c r="D10" s="18" t="n">
-        <f aca="false">Programme!$G$57</f>
+        <f aca="false">Programme!$G$61</f>
         <v>4.1</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -5733,7 +5767,7 @@
         <v>96</v>
       </c>
       <c r="D11" s="18" t="n">
-        <f aca="false">Programme!$G$58</f>
+        <f aca="false">Programme!$G$62</f>
         <v>4.1</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -5758,7 +5792,7 @@
         <v>96</v>
       </c>
       <c r="D12" s="18" t="n">
-        <f aca="false">Programme!$G$59</f>
+        <f aca="false">Programme!$G$63</f>
         <v>4.1</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -5783,7 +5817,7 @@
         <v>96</v>
       </c>
       <c r="D13" s="18" t="n">
-        <f aca="false">Programme!$G$60</f>
+        <f aca="false">Programme!$G$64</f>
         <v>4.1</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -5808,7 +5842,7 @@
         <v>96</v>
       </c>
       <c r="D14" s="18" t="n">
-        <f aca="false">Programme!$G$61</f>
+        <f aca="false">Programme!$G$65</f>
         <v>4.1</v>
       </c>
       <c r="E14" s="18" t="n">
@@ -5833,7 +5867,7 @@
         <v>96</v>
       </c>
       <c r="D15" s="18" t="n">
-        <f aca="false">Programme!$G$62</f>
+        <f aca="false">Programme!$G$66</f>
         <v>4.1</v>
       </c>
       <c r="E15" s="18" t="n">
@@ -5858,7 +5892,7 @@
         <v>96</v>
       </c>
       <c r="D16" s="18" t="n">
-        <f aca="false">Programme!$G$63</f>
+        <f aca="false">Programme!$G$67</f>
         <v>4.1</v>
       </c>
       <c r="E16" s="18" t="n">
@@ -5883,7 +5917,7 @@
         <v>118</v>
       </c>
       <c r="D17" s="18" t="n">
-        <f aca="false">Programme!$G$64</f>
+        <f aca="false">Programme!$G$68</f>
         <v>36</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -5908,7 +5942,7 @@
         <v>96</v>
       </c>
       <c r="D18" s="18" t="n">
-        <f aca="false">Programme!$G$65</f>
+        <f aca="false">Programme!$G$69</f>
         <v>4.1</v>
       </c>
       <c r="E18" s="18" t="n">
@@ -5933,7 +5967,7 @@
         <v>124</v>
       </c>
       <c r="D19" s="18" t="n">
-        <f aca="false">Programme!$G$66</f>
+        <f aca="false">Programme!$G$70</f>
         <v>4</v>
       </c>
       <c r="E19" s="18" t="n">
@@ -5958,7 +5992,7 @@
         <v>96</v>
       </c>
       <c r="D20" s="18" t="n">
-        <f aca="false">Programme!$G$67</f>
+        <f aca="false">Programme!$G$71</f>
         <v>4.1</v>
       </c>
       <c r="E20" s="18" t="n">
@@ -5983,7 +6017,7 @@
         <v>96</v>
       </c>
       <c r="D21" s="18" t="n">
-        <f aca="false">Programme!$G$68</f>
+        <f aca="false">Programme!$G$72</f>
         <v>4.1</v>
       </c>
       <c r="E21" s="18" t="n">
@@ -6978,7 +7012,7 @@
         <v>162</v>
       </c>
       <c r="D74" s="18" t="n">
-        <f aca="false">Programme!$G$69</f>
+        <f aca="false">Programme!$G$73</f>
         <v>47</v>
       </c>
       <c r="E74" s="18" t="n">
@@ -7003,7 +7037,7 @@
         <v>162</v>
       </c>
       <c r="D75" s="18" t="n">
-        <f aca="false">Programme!$G$70</f>
+        <f aca="false">Programme!$G$74</f>
         <v>47</v>
       </c>
       <c r="E75" s="18" t="n">
@@ -7052,7 +7086,7 @@
         <v>242</v>
       </c>
       <c r="D77" s="18" t="n">
-        <f aca="false">Programme!$G$71</f>
+        <f aca="false">Programme!$G$75</f>
         <v>4</v>
       </c>
       <c r="E77" s="18" t="n">
@@ -7101,7 +7135,7 @@
         <v>248</v>
       </c>
       <c r="D79" s="18" t="n">
-        <f aca="false">Programme!$G$72</f>
+        <f aca="false">Programme!$G$76</f>
         <v>4</v>
       </c>
       <c r="E79" s="18" t="n">
@@ -7126,7 +7160,7 @@
         <v>96</v>
       </c>
       <c r="D80" s="18" t="n">
-        <f aca="false">Programme!$G$73</f>
+        <f aca="false">Programme!$G$77</f>
         <v>3.8</v>
       </c>
       <c r="E80" s="18" t="n">
@@ -7151,7 +7185,7 @@
         <v>96</v>
       </c>
       <c r="D81" s="18" t="n">
-        <f aca="false">Programme!$G$74</f>
+        <f aca="false">Programme!$G$78</f>
         <v>4.1</v>
       </c>
       <c r="E81" s="18" t="n">
@@ -7176,7 +7210,7 @@
         <v>96</v>
       </c>
       <c r="D82" s="18" t="n">
-        <f aca="false">Programme!$G$75</f>
+        <f aca="false">Programme!$G$79</f>
         <v>4.1</v>
       </c>
       <c r="E82" s="18" t="n">
@@ -7201,7 +7235,7 @@
         <v>261</v>
       </c>
       <c r="D83" s="18" t="n">
-        <f aca="false">Programme!$G$76</f>
+        <f aca="false">Programme!$G$80</f>
         <v>10.5</v>
       </c>
       <c r="E83" s="18" t="n">
@@ -7226,7 +7260,7 @@
         <v>96</v>
       </c>
       <c r="D84" s="18" t="n">
-        <f aca="false">Programme!$G$77</f>
+        <f aca="false">Programme!$G$81</f>
         <v>2.1</v>
       </c>
       <c r="E84" s="18" t="n">
@@ -7299,7 +7333,7 @@
         <v>248</v>
       </c>
       <c r="D87" s="18" t="n">
-        <f aca="false">Programme!$G$78</f>
+        <f aca="false">Programme!$G$82</f>
         <v>4.2</v>
       </c>
       <c r="E87" s="18" t="n">
@@ -7490,7 +7524,7 @@
         <v>207</v>
       </c>
       <c r="D100" s="18" t="n">
-        <f aca="false">Programme!$G$79</f>
+        <f aca="false">Programme!$G$83</f>
         <v>3774</v>
       </c>
       <c r="E100" s="18" t="n">
@@ -7515,7 +7549,7 @@
         <v>162</v>
       </c>
       <c r="D101" s="18" t="n">
-        <f aca="false">Programme!$G$80</f>
+        <f aca="false">Programme!$G$84</f>
         <v>7</v>
       </c>
       <c r="E101" s="18" t="n">
@@ -7540,7 +7574,7 @@
         <v>292</v>
       </c>
       <c r="D102" s="18" t="n">
-        <f aca="false">Programme!$G$81</f>
+        <f aca="false">Programme!$G$85</f>
         <v>1</v>
       </c>
       <c r="E102" s="18" t="n">
@@ -7565,7 +7599,7 @@
         <v>141</v>
       </c>
       <c r="D103" s="18" t="n">
-        <f aca="false">Programme!$G$82</f>
+        <f aca="false">Programme!$G$86</f>
         <v>6</v>
       </c>
       <c r="E103" s="18" t="n">
@@ -7590,7 +7624,7 @@
         <v>207</v>
       </c>
       <c r="D104" s="18" t="n">
-        <f aca="false">Programme!$G$83</f>
+        <f aca="false">Programme!$G$87</f>
         <v>377</v>
       </c>
       <c r="E104" s="18" t="n">
@@ -7783,7 +7817,7 @@
         <v>162</v>
       </c>
       <c r="D112" s="18" t="n">
-        <f aca="false">Programme!$G$84</f>
+        <f aca="false">Programme!$G$88</f>
         <v>8</v>
       </c>
       <c r="E112" s="18" t="n">
@@ -7808,7 +7842,7 @@
         <v>141</v>
       </c>
       <c r="D113" s="18" t="n">
-        <f aca="false">Programme!$G$85</f>
+        <f aca="false">Programme!$G$89</f>
         <v>12</v>
       </c>
       <c r="E113" s="18" t="n">
@@ -7857,7 +7891,7 @@
         <v>162</v>
       </c>
       <c r="D115" s="18" t="n">
-        <f aca="false">Programme!$G$86</f>
+        <f aca="false">Programme!$G$90</f>
         <v>5</v>
       </c>
       <c r="E115" s="18" t="n">
@@ -8002,7 +8036,7 @@
         <v>162</v>
       </c>
       <c r="D121" s="18" t="n">
-        <f aca="false">Programme!$G$87</f>
+        <f aca="false">Programme!$G$91</f>
         <v>8</v>
       </c>
       <c r="E121" s="18" t="n">
@@ -12209,7 +12243,7 @@
       </c>
       <c r="J35" s="19"/>
     </row>
-    <row r="36" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="93" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="16" t="s">
         <v>742</v>
       </c>
@@ -12242,24 +12276,24 @@
       </c>
       <c r="J36" s="19"/>
     </row>
-    <row r="37" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="93" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="16" t="s">
         <v>745</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>746</v>
       </c>
-      <c r="C37" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(D27,1,"0000100",$C$14)</f>
-        <v>46343</v>
-      </c>
-      <c r="D37" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(C37,E37-1,"0000100",$C$14)</f>
-        <v>46350</v>
-      </c>
-      <c r="E37" s="54" t="n">
-        <f aca="false">$E$177</f>
-        <v>7</v>
+      <c r="C37" s="58" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
+      </c>
+      <c r="D37" s="58" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
+      </c>
+      <c r="E37" s="54" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
       </c>
       <c r="F37" s="58" t="n">
         <f aca="false">WORKDAY.INTL(G27,1,"0000100",$C$14)</f>
@@ -12270,7 +12304,7 @@
         <v>46328</v>
       </c>
       <c r="H37" s="54" t="n">
-        <f aca="false">E37</f>
+        <f aca="false">$E$177</f>
         <v>7</v>
       </c>
       <c r="I37" s="19" t="s">
@@ -12285,16 +12319,17 @@
       <c r="B38" s="17" t="s">
         <v>749</v>
       </c>
-      <c r="C38" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(MAX(D37,D33),1,"0000100",$C$14)</f>
-        <v>46361</v>
-      </c>
-      <c r="D38" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(C38,E38-1,"0000100",$C$14)</f>
-        <v>46363</v>
-      </c>
-      <c r="E38" s="54" t="n">
-        <v>3</v>
+      <c r="C38" s="58" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
+      </c>
+      <c r="D38" s="58" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
+      </c>
+      <c r="E38" s="54" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
       </c>
       <c r="F38" s="58" t="n">
         <f aca="false">WORKDAY.INTL(MAX(G37,G33),1,"0000100",$C$14)</f>
@@ -12305,7 +12340,6 @@
         <v>46344</v>
       </c>
       <c r="H38" s="54" t="n">
-        <f aca="false">E38</f>
         <v>3</v>
       </c>
       <c r="I38" s="19" t="s">
@@ -12320,17 +12354,17 @@
       <c r="B39" s="17" t="s">
         <v>752</v>
       </c>
-      <c r="C39" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(D38,1,"0000100",$C$14)</f>
-        <v>46364</v>
-      </c>
-      <c r="D39" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(C39,E39-1,"0000100",$C$14)</f>
-        <v>46371</v>
-      </c>
-      <c r="E39" s="54" t="n">
-        <f aca="false">$E$178</f>
-        <v>7</v>
+      <c r="C39" s="58" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
+      </c>
+      <c r="D39" s="58" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
+      </c>
+      <c r="E39" s="54" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
       </c>
       <c r="F39" s="58" t="n">
         <f aca="false">WORKDAY.INTL(G38,1,"0000100",$C$14)</f>
@@ -12341,7 +12375,7 @@
         <v>46352</v>
       </c>
       <c r="H39" s="54" t="n">
-        <f aca="false">E39</f>
+        <f aca="false">$E$178</f>
         <v>7</v>
       </c>
       <c r="I39" s="19" t="s">
@@ -12349,23 +12383,24 @@
       </c>
       <c r="J39" s="19"/>
     </row>
-    <row r="40" customFormat="false" ht="93" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="16" t="s">
         <v>754</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>755</v>
       </c>
-      <c r="C40" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(D35,1,"0000100",$C$14)</f>
-        <v>46365</v>
-      </c>
-      <c r="D40" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(C40,E40-1,"0000100",$C$14)</f>
-        <v>46368</v>
-      </c>
-      <c r="E40" s="54" t="n">
-        <v>3</v>
+      <c r="C40" s="58" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
+      </c>
+      <c r="D40" s="58" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
+      </c>
+      <c r="E40" s="54" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
       </c>
       <c r="F40" s="58" t="n">
         <f aca="false">WORKDAY.INTL(G35,1,"0000100",$C$14)</f>
@@ -12376,7 +12411,6 @@
         <v>46368</v>
       </c>
       <c r="H40" s="54" t="n">
-        <f aca="false">E40</f>
         <v>3</v>
       </c>
       <c r="I40" s="19" t="s">
@@ -12384,23 +12418,24 @@
       </c>
       <c r="J40" s="19"/>
     </row>
-    <row r="41" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
         <v>757</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="C41" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(MAX(D35,D39,D40),1,"0000100",$C$14)</f>
-        <v>46372</v>
-      </c>
-      <c r="D41" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(C41,E41-1,"0000100",$C$14)</f>
-        <v>46375</v>
-      </c>
-      <c r="E41" s="54" t="n">
-        <v>3</v>
+      <c r="C41" s="58" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
+      </c>
+      <c r="D41" s="58" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
+      </c>
+      <c r="E41" s="54" t="str">
+        <f aca="false">G36</f>
+        <v>-</v>
       </c>
       <c r="F41" s="58" t="n">
         <f aca="false">WORKDAY.INTL(MAX(G35,G39,G40),1,"0000100",$C$14)</f>
@@ -12411,7 +12446,6 @@
         <v>46371</v>
       </c>
       <c r="H41" s="54" t="n">
-        <f aca="false">E41</f>
         <v>3</v>
       </c>
       <c r="I41" s="19" t="s">
@@ -12427,12 +12461,12 @@
         <v>761</v>
       </c>
       <c r="C42" s="58" t="n">
-        <f aca="false">D41</f>
-        <v>46375</v>
+        <f aca="false">$D$179</f>
+        <v>46372</v>
       </c>
       <c r="D42" s="58" t="n">
         <f aca="false">C42</f>
-        <v>46375</v>
+        <v>46372</v>
       </c>
       <c r="E42" s="54" t="s">
         <v>737</v>
@@ -12453,7 +12487,7 @@
       </c>
       <c r="J42" s="19"/>
     </row>
-    <row r="43" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="16" t="s">
         <v>763</v>
       </c>
@@ -12461,15 +12495,15 @@
         <v>764</v>
       </c>
       <c r="C43" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(D42,1,"0000100",$C$14)</f>
-        <v>46376</v>
+        <f aca="false">$C$181</f>
+        <v>46373</v>
       </c>
       <c r="D43" s="58" t="n">
-        <f aca="false">WORKDAY.INTL(C43,E43-1,"0000100",$C$14)</f>
-        <v>46383</v>
+        <f aca="false">$D$181</f>
+        <v>46380</v>
       </c>
       <c r="E43" s="54" t="n">
-        <f aca="false">$E$181</f>
+        <f aca="false">NETWORKDAYS.INTL(C43,D43,"0000100",$C$14)</f>
         <v>7</v>
       </c>
       <c r="F43" s="58" t="n">
@@ -12503,7 +12537,7 @@
       <c r="I44" s="23"/>
       <c r="J44" s="23"/>
     </row>
-    <row r="45" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="118.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
         <v>767</v>
       </c>
@@ -12516,11 +12550,11 @@
       </c>
       <c r="D45" s="58" t="n">
         <f aca="false">D43</f>
-        <v>46383</v>
+        <v>46380</v>
       </c>
       <c r="E45" s="54" t="n">
         <f aca="false">D45-C45+1</f>
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F45" s="58" t="n">
         <f aca="false">F20</f>
@@ -12552,11 +12586,11 @@
       </c>
       <c r="D46" s="58" t="n">
         <f aca="false">D42</f>
-        <v>46375</v>
+        <v>46372</v>
       </c>
       <c r="E46" s="54" t="n">
         <f aca="false">D46-C46+1</f>
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F46" s="58" t="n">
         <f aca="false">F20</f>
@@ -12755,244 +12789,200 @@
       </c>
       <c r="J51" s="19"/>
     </row>
-    <row r="53" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15" t="s">
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="23"/>
+      <c r="B52" s="23" t="s">
         <v>788</v>
       </c>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-    </row>
-    <row r="54" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="11" t="s">
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="23"/>
+      <c r="I52" s="23"/>
+      <c r="J52" s="23"/>
+    </row>
+    <row r="53" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="16" t="s">
         <v>789</v>
       </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-    </row>
-    <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="13" t="s">
+      <c r="B53" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="C53" s="58" t="n">
+        <f aca="false">C20</f>
+        <v>46256</v>
+      </c>
+      <c r="D53" s="58" t="n">
+        <f aca="false">WORKDAY.INTL(WORKDAY.INTL(MAX(D35,WORKDAY.INTL(WORKDAY.INTL(WORKDAY.INTL(WORKDAY.INTL(MAX(WORKDAY.INTL(WORKDAY.INTL(D27,1,"0000100",$C$14),7-1,"0000100",$C$14),D33),1,"0000100",$C$14),3-1,"0000100",$C$14),1,"0000100",$C$14),7-1,"0000100",$C$14),WORKDAY.INTL(WORKDAY.INTL(D35,1,"0000100",$C$14),3-1,"0000100",$C$14)),1,"0000100",$C$14),3-1,"0000100",$C$14)</f>
+        <v>46375</v>
+      </c>
+      <c r="E53" s="54" t="n">
+        <f aca="false">D53-C53+1</f>
+        <v>120</v>
+      </c>
+      <c r="F53" s="58" t="s">
+        <v>737</v>
+      </c>
+      <c r="G53" s="58" t="s">
+        <v>737</v>
+      </c>
+      <c r="H53" s="54" t="s">
+        <v>737</v>
+      </c>
+      <c r="I53" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="J53" s="19"/>
+    </row>
+    <row r="54" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>793</v>
+      </c>
+      <c r="C54" s="58" t="n">
+        <f aca="false">F20</f>
+        <v>46256</v>
+      </c>
+      <c r="D54" s="58" t="n">
+        <f aca="false">WORKDAY.INTL(WORKDAY.INTL(WORKDAY.INTL(WORKDAY.INTL(MAX(G35,WORKDAY.INTL(WORKDAY.INTL(WORKDAY.INTL(WORKDAY.INTL(WORKDAY.INTL(WORKDAY.INTL(G35,1,"0000100",$C$14),7-1,"0000100",$C$14),1,"0000100",$C$14),3-1,"0000100",$C$14),1,"0000100",$C$14),7-1,"0000100",$C$14),WORKDAY.INTL(WORKDAY.INTL(G35,1,"0000100",$C$14),3-1,"0000100",$C$14)),1,"0000100",$C$14),3-1,"0000100",$C$14),1,"0000100",$C$14),7-1,"0000100",$C$14)</f>
+        <v>46396</v>
+      </c>
+      <c r="E54" s="54" t="n">
+        <f aca="false">D54-C54+1</f>
+        <v>141</v>
+      </c>
+      <c r="F54" s="58" t="s">
+        <v>737</v>
+      </c>
+      <c r="G54" s="58" t="s">
+        <v>737</v>
+      </c>
+      <c r="H54" s="54" t="s">
+        <v>737</v>
+      </c>
+      <c r="I54" s="19" t="s">
+        <v>794</v>
+      </c>
+      <c r="J54" s="19"/>
+    </row>
+    <row r="55" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>796</v>
+      </c>
+      <c r="C55" s="59" t="n">
+        <f aca="false">E54-H45</f>
+        <v>17</v>
+      </c>
+      <c r="D55" s="58" t="s">
+        <v>737</v>
+      </c>
+      <c r="E55" s="18" t="n">
+        <f aca="false">D60*(ROUND((H45+C55)/$C$15,1)-G60)+D61*(ROUND((H45+C55)/$C$15,1)-G61)+D62*(ROUND((H45+C55)/$C$15,1)-G62)+D63*(ROUND((H45+C55)/$C$15,1)-G63)+D64*(ROUND((H45+C55)/$C$15,1)-G64)+D65*(ROUND((H45+C55)/$C$15,1)-G65)+D66*(ROUND((H45+C55)/$C$15,1)-G66)+D67*(ROUND((H45+C55)/$C$15,1)-G67)+D69*(ROUND((H45+C55)/$C$15,1)-G69)+D71*(ROUND((H45+C55)/$C$15,1)-G71)+D72*(ROUND((H45+C55)/$C$15,1)-G72)+D77*(ROUND((H46+C55)/$C$15,1)-G77)+D78*(ROUND((H45+C55)/$C$15,1)-G78)+D79*(ROUND((H45+C55)/$C$15,1)-G79)+D68*(2*ROUNDUP((H45+C55)/7,0)-G68)</f>
+        <v>42475</v>
+      </c>
+      <c r="F55" s="58" t="s">
+        <v>737</v>
+      </c>
+      <c r="G55" s="58" t="s">
+        <v>737</v>
+      </c>
+      <c r="H55" s="54" t="s">
+        <v>737</v>
+      </c>
+      <c r="I55" s="19" t="s">
+        <v>797</v>
+      </c>
+      <c r="J55" s="19"/>
+    </row>
+    <row r="57" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
+        <v>798</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+    </row>
+    <row r="58" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="11" t="s">
+        <v>799</v>
+      </c>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+    </row>
+    <row r="59" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="B55" s="13" t="s">
-        <v>790</v>
-      </c>
-      <c r="C55" s="13" t="s">
+      <c r="B59" s="13" t="s">
+        <v>800</v>
+      </c>
+      <c r="C59" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D59" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E55" s="13" t="s">
-        <v>791</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>792</v>
-      </c>
-      <c r="G55" s="13" t="s">
-        <v>793</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>794</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>795</v>
-      </c>
-      <c r="J55" s="13" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="16" t="s">
+      <c r="E59" s="13" t="s">
+        <v>801</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>802</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>803</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>804</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>805</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B56" s="17" t="str">
+      <c r="B60" s="17" t="str">
         <f aca="false">'Build-Up'!B9</f>
         <v>Site engineer - dedicated to the tank site</v>
       </c>
-      <c r="C56" s="16" t="str">
+      <c r="C60" s="16" t="str">
         <f aca="false">'Build-Up'!C9</f>
         <v>month</v>
       </c>
-      <c r="D56" s="18" t="n">
+      <c r="D60" s="18" t="n">
         <f aca="false">'Build-Up'!E9</f>
         <v>12000</v>
       </c>
-      <c r="E56" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F56" s="18" t="n">
-        <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
-      </c>
-      <c r="G56" s="20" t="n">
-        <f aca="false">ROUND(H45/$C$15,1)</f>
-        <v>4.1</v>
-      </c>
-      <c r="H56" s="18" t="n">
-        <f aca="false">ROUND(F56*D56,2)</f>
-        <v>50400</v>
-      </c>
-      <c r="I56" s="18" t="n">
-        <f aca="false">ROUND(G56*D56,2)</f>
-        <v>49200</v>
-      </c>
-      <c r="J56" s="19" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B57" s="17" t="str">
-        <f aca="false">'Build-Up'!B10</f>
-        <v>HSE officer - dedicated</v>
-      </c>
-      <c r="C57" s="16" t="str">
-        <f aca="false">'Build-Up'!C10</f>
-        <v>month</v>
-      </c>
-      <c r="D57" s="18" t="n">
-        <f aca="false">'Build-Up'!E10</f>
-        <v>10000</v>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F57" s="18" t="n">
-        <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
-      </c>
-      <c r="G57" s="20" t="n">
-        <f aca="false">ROUND(H45/$C$15,1)</f>
-        <v>4.1</v>
-      </c>
-      <c r="H57" s="18" t="n">
-        <f aca="false">ROUND(F57*D57,2)</f>
-        <v>42000</v>
-      </c>
-      <c r="I57" s="18" t="n">
-        <f aca="false">ROUND(G57*D57,2)</f>
-        <v>41000</v>
-      </c>
-      <c r="J57" s="19" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B58" s="17" t="str">
-        <f aca="false">'Build-Up'!B11</f>
-        <v>QA/QC inspector - dedicated (daily inspections, ITPs and WIRs during erection)</v>
-      </c>
-      <c r="C58" s="16" t="str">
-        <f aca="false">'Build-Up'!C11</f>
-        <v>month</v>
-      </c>
-      <c r="D58" s="18" t="n">
-        <f aca="false">'Build-Up'!E11</f>
-        <v>10000</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F58" s="18" t="n">
-        <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
-      </c>
-      <c r="G58" s="20" t="n">
-        <f aca="false">ROUND(H45/$C$15,1)</f>
-        <v>4.1</v>
-      </c>
-      <c r="H58" s="18" t="n">
-        <f aca="false">ROUND(F58*D58,2)</f>
-        <v>42000</v>
-      </c>
-      <c r="I58" s="18" t="n">
-        <f aca="false">ROUND(G58*D58,2)</f>
-        <v>41000</v>
-      </c>
-      <c r="J58" s="19" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B59" s="17" t="str">
-        <f aca="false">'Build-Up'!B12</f>
-        <v>Works foreman - dedicated</v>
-      </c>
-      <c r="C59" s="16" t="str">
-        <f aca="false">'Build-Up'!C12</f>
-        <v>month</v>
-      </c>
-      <c r="D59" s="18" t="n">
-        <f aca="false">'Build-Up'!E12</f>
-        <v>8000</v>
-      </c>
-      <c r="E59" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F59" s="18" t="n">
-        <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
-      </c>
-      <c r="G59" s="20" t="n">
-        <f aca="false">ROUND(H45/$C$15,1)</f>
-        <v>4.1</v>
-      </c>
-      <c r="H59" s="18" t="n">
-        <f aca="false">ROUND(F59*D59,2)</f>
-        <v>33600</v>
-      </c>
-      <c r="I59" s="18" t="n">
-        <f aca="false">ROUND(G59*D59,2)</f>
-        <v>32800</v>
-      </c>
-      <c r="J59" s="19" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B60" s="17" t="str">
-        <f aca="false">'Build-Up'!B13</f>
-        <v>Storekeeper / timekeeper</v>
-      </c>
-      <c r="C60" s="16" t="str">
-        <f aca="false">'Build-Up'!C13</f>
-        <v>month</v>
-      </c>
-      <c r="D60" s="18" t="n">
-        <f aca="false">'Build-Up'!E13</f>
-        <v>4000</v>
-      </c>
       <c r="E60" s="18" t="n">
         <v>3</v>
       </c>
       <c r="F60" s="18" t="n">
         <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G60" s="20" t="n">
         <f aca="false">ROUND(H45/$C$15,1)</f>
@@ -13000,38 +12990,38 @@
       </c>
       <c r="H60" s="18" t="n">
         <f aca="false">ROUND(F60*D60,2)</f>
-        <v>16800</v>
+        <v>49200</v>
       </c>
       <c r="I60" s="18" t="n">
         <f aca="false">ROUND(G60*D60,2)</f>
-        <v>16400</v>
+        <v>49200</v>
       </c>
       <c r="J60" s="19" t="s">
-        <v>797</v>
+        <v>807</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="16" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B61" s="17" t="str">
-        <f aca="false">'Build-Up'!B14</f>
-        <v>Site office porta cabin, air-conditioned, rental with electricity connection and maintenance</v>
+        <f aca="false">'Build-Up'!B10</f>
+        <v>HSE officer - dedicated</v>
       </c>
       <c r="C61" s="16" t="str">
-        <f aca="false">'Build-Up'!C14</f>
+        <f aca="false">'Build-Up'!C10</f>
         <v>month</v>
       </c>
       <c r="D61" s="18" t="n">
-        <f aca="false">'Build-Up'!E14</f>
-        <v>2200</v>
+        <f aca="false">'Build-Up'!E10</f>
+        <v>10000</v>
       </c>
       <c r="E61" s="18" t="n">
         <v>3</v>
       </c>
       <c r="F61" s="18" t="n">
         <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G61" s="20" t="n">
         <f aca="false">ROUND(H45/$C$15,1)</f>
@@ -13039,38 +13029,38 @@
       </c>
       <c r="H61" s="18" t="n">
         <f aca="false">ROUND(F61*D61,2)</f>
-        <v>9240</v>
+        <v>41000</v>
       </c>
       <c r="I61" s="18" t="n">
         <f aca="false">ROUND(G61*D61,2)</f>
-        <v>9020</v>
+        <v>41000</v>
       </c>
       <c r="J61" s="19" t="s">
-        <v>798</v>
+        <v>807</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="16" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B62" s="17" t="str">
-        <f aca="false">'Build-Up'!B15</f>
-        <v>Rest and welfare porta cabin, air-conditioned, rental with electricity connection and maintenance</v>
+        <f aca="false">'Build-Up'!B11</f>
+        <v>QA/QC inspector - dedicated (daily inspections, ITPs and WIRs during erection)</v>
       </c>
       <c r="C62" s="16" t="str">
-        <f aca="false">'Build-Up'!C15</f>
+        <f aca="false">'Build-Up'!C11</f>
         <v>month</v>
       </c>
       <c r="D62" s="18" t="n">
-        <f aca="false">'Build-Up'!E15</f>
-        <v>2200</v>
+        <f aca="false">'Build-Up'!E11</f>
+        <v>10000</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>3</v>
       </c>
       <c r="F62" s="18" t="n">
         <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G62" s="20" t="n">
         <f aca="false">ROUND(H45/$C$15,1)</f>
@@ -13078,38 +13068,38 @@
       </c>
       <c r="H62" s="18" t="n">
         <f aca="false">ROUND(F62*D62,2)</f>
-        <v>9240</v>
+        <v>41000</v>
       </c>
       <c r="I62" s="18" t="n">
         <f aca="false">ROUND(G62*D62,2)</f>
-        <v>9020</v>
+        <v>41000</v>
       </c>
       <c r="J62" s="19" t="s">
-        <v>798</v>
+        <v>807</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="16" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B63" s="17" t="str">
-        <f aca="false">'Build-Up'!B16</f>
-        <v>WC unit, rental with servicing</v>
+        <f aca="false">'Build-Up'!B12</f>
+        <v>Works foreman - dedicated</v>
       </c>
       <c r="C63" s="16" t="str">
-        <f aca="false">'Build-Up'!C16</f>
+        <f aca="false">'Build-Up'!C12</f>
         <v>month</v>
       </c>
       <c r="D63" s="18" t="n">
-        <f aca="false">'Build-Up'!E16</f>
-        <v>1300</v>
+        <f aca="false">'Build-Up'!E12</f>
+        <v>8000</v>
       </c>
       <c r="E63" s="18" t="n">
         <v>3</v>
       </c>
       <c r="F63" s="18" t="n">
         <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G63" s="20" t="n">
         <f aca="false">ROUND(H45/$C$15,1)</f>
@@ -13117,77 +13107,77 @@
       </c>
       <c r="H63" s="18" t="n">
         <f aca="false">ROUND(F63*D63,2)</f>
-        <v>5460</v>
+        <v>32800</v>
       </c>
       <c r="I63" s="18" t="n">
         <f aca="false">ROUND(G63*D63,2)</f>
-        <v>5330</v>
+        <v>32800</v>
       </c>
       <c r="J63" s="19" t="s">
-        <v>798</v>
+        <v>807</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="16" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B64" s="17" t="str">
-        <f aca="false">'Build-Up'!B17</f>
-        <v>Site water supply - tankered deliveries for welfare and general site use, whole period</v>
+        <f aca="false">'Build-Up'!B13</f>
+        <v>Storekeeper / timekeeper</v>
       </c>
       <c r="C64" s="16" t="str">
-        <f aca="false">'Build-Up'!C17</f>
-        <v>delivery</v>
+        <f aca="false">'Build-Up'!C13</f>
+        <v>month</v>
       </c>
       <c r="D64" s="18" t="n">
-        <f aca="false">'Build-Up'!E17</f>
-        <v>350</v>
+        <f aca="false">'Build-Up'!E13</f>
+        <v>4000</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F64" s="18" t="n">
-        <f aca="false">2*ROUNDUP(E45/7,0)</f>
-        <v>38</v>
+        <f aca="false">ROUND(E45/$C$15,1)</f>
+        <v>4.1</v>
       </c>
       <c r="G64" s="20" t="n">
-        <f aca="false">2*ROUNDUP(H45/7,0)</f>
-        <v>36</v>
+        <f aca="false">ROUND(H45/$C$15,1)</f>
+        <v>4.1</v>
       </c>
       <c r="H64" s="18" t="n">
         <f aca="false">ROUND(F64*D64,2)</f>
-        <v>13300</v>
+        <v>16400</v>
       </c>
       <c r="I64" s="18" t="n">
         <f aca="false">ROUND(G64*D64,2)</f>
-        <v>12600</v>
+        <v>16400</v>
       </c>
       <c r="J64" s="19" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="16" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B65" s="17" t="str">
-        <f aca="false">'Build-Up'!B18</f>
-        <v>Site water storage tank, hire</v>
+        <f aca="false">'Build-Up'!B14</f>
+        <v>Site office porta cabin, air-conditioned, rental with electricity connection and maintenance</v>
       </c>
       <c r="C65" s="16" t="str">
-        <f aca="false">'Build-Up'!C18</f>
+        <f aca="false">'Build-Up'!C14</f>
         <v>month</v>
       </c>
       <c r="D65" s="18" t="n">
-        <f aca="false">'Build-Up'!E18</f>
-        <v>350</v>
+        <f aca="false">'Build-Up'!E14</f>
+        <v>2200</v>
       </c>
       <c r="E65" s="18" t="n">
         <v>3</v>
       </c>
       <c r="F65" s="18" t="n">
         <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G65" s="20" t="n">
         <f aca="false">ROUND(H45/$C$15,1)</f>
@@ -13195,77 +13185,77 @@
       </c>
       <c r="H65" s="18" t="n">
         <f aca="false">ROUND(F65*D65,2)</f>
-        <v>1470</v>
+        <v>9020</v>
       </c>
       <c r="I65" s="18" t="n">
         <f aca="false">ROUND(G65*D65,2)</f>
-        <v>1435</v>
+        <v>9020</v>
       </c>
       <c r="J65" s="19" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="16" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B66" s="17" t="str">
-        <f aca="false">'Build-Up'!B19</f>
-        <v>Storage containers, 2 No. for the panel storage window (RFP Scope of Works, work package 1 - pre-construction and setup: safe storage of panels)</v>
+        <f aca="false">'Build-Up'!B15</f>
+        <v>Rest and welfare porta cabin, air-conditioned, rental with electricity connection and maintenance</v>
       </c>
       <c r="C66" s="16" t="str">
-        <f aca="false">'Build-Up'!C19</f>
-        <v>container-month</v>
+        <f aca="false">'Build-Up'!C15</f>
+        <v>month</v>
       </c>
       <c r="D66" s="18" t="n">
-        <f aca="false">'Build-Up'!E19</f>
-        <v>1200</v>
+        <f aca="false">'Build-Up'!E15</f>
+        <v>2200</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F66" s="18" t="n">
-        <f aca="false">2*ROUND(E51/$C$15,1)</f>
-        <v>5.6</v>
+        <f aca="false">ROUND(E45/$C$15,1)</f>
+        <v>4.1</v>
       </c>
       <c r="G66" s="20" t="n">
-        <f aca="false">2*ROUND(H51/$C$15,1)</f>
-        <v>4</v>
+        <f aca="false">ROUND(H45/$C$15,1)</f>
+        <v>4.1</v>
       </c>
       <c r="H66" s="18" t="n">
         <f aca="false">ROUND(F66*D66,2)</f>
-        <v>6720</v>
+        <v>9020</v>
       </c>
       <c r="I66" s="18" t="n">
         <f aca="false">ROUND(G66*D66,2)</f>
-        <v>4800</v>
+        <v>9020</v>
       </c>
       <c r="J66" s="19" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="16" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B67" s="17" t="str">
-        <f aca="false">'Build-Up'!B20</f>
-        <v>Workforce transport to the tank site, daily bus</v>
+        <f aca="false">'Build-Up'!B16</f>
+        <v>WC unit, rental with servicing</v>
       </c>
       <c r="C67" s="16" t="str">
-        <f aca="false">'Build-Up'!C20</f>
+        <f aca="false">'Build-Up'!C16</f>
         <v>month</v>
       </c>
       <c r="D67" s="18" t="n">
-        <f aca="false">'Build-Up'!E20</f>
-        <v>4000</v>
+        <f aca="false">'Build-Up'!E16</f>
+        <v>1300</v>
       </c>
       <c r="E67" s="18" t="n">
         <v>3</v>
       </c>
       <c r="F67" s="18" t="n">
         <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G67" s="20" t="n">
         <f aca="false">ROUND(H45/$C$15,1)</f>
@@ -13273,888 +13263,956 @@
       </c>
       <c r="H67" s="18" t="n">
         <f aca="false">ROUND(F67*D67,2)</f>
-        <v>16800</v>
+        <v>5330</v>
       </c>
       <c r="I67" s="18" t="n">
         <f aca="false">ROUND(G67*D67,2)</f>
-        <v>16400</v>
+        <v>5330</v>
       </c>
       <c r="J67" s="19" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B68" s="17" t="str">
+        <f aca="false">'Build-Up'!B17</f>
+        <v>Site water supply - tankered deliveries for welfare and general site use, whole period</v>
+      </c>
+      <c r="C68" s="16" t="str">
+        <f aca="false">'Build-Up'!C17</f>
+        <v>delivery</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <f aca="false">'Build-Up'!E17</f>
+        <v>350</v>
+      </c>
+      <c r="E68" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="F68" s="18" t="n">
+        <f aca="false">2*ROUNDUP(E45/7,0)</f>
+        <v>36</v>
+      </c>
+      <c r="G68" s="20" t="n">
+        <f aca="false">2*ROUNDUP(H45/7,0)</f>
+        <v>36</v>
+      </c>
+      <c r="H68" s="18" t="n">
+        <f aca="false">ROUND(F68*D68,2)</f>
+        <v>12600</v>
+      </c>
+      <c r="I68" s="18" t="n">
+        <f aca="false">ROUND(G68*D68,2)</f>
+        <v>12600</v>
+      </c>
+      <c r="J68" s="19" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" s="17" t="str">
+        <f aca="false">'Build-Up'!B18</f>
+        <v>Site water storage tank, hire</v>
+      </c>
+      <c r="C69" s="16" t="str">
+        <f aca="false">'Build-Up'!C18</f>
+        <v>month</v>
+      </c>
+      <c r="D69" s="18" t="n">
+        <f aca="false">'Build-Up'!E18</f>
+        <v>350</v>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" s="18" t="n">
+        <f aca="false">ROUND(E45/$C$15,1)</f>
+        <v>4.1</v>
+      </c>
+      <c r="G69" s="20" t="n">
+        <f aca="false">ROUND(H45/$C$15,1)</f>
+        <v>4.1</v>
+      </c>
+      <c r="H69" s="18" t="n">
+        <f aca="false">ROUND(F69*D69,2)</f>
+        <v>1435</v>
+      </c>
+      <c r="I69" s="18" t="n">
+        <f aca="false">ROUND(G69*D69,2)</f>
+        <v>1435</v>
+      </c>
+      <c r="J69" s="19" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B70" s="17" t="str">
+        <f aca="false">'Build-Up'!B19</f>
+        <v>Storage containers, 2 No. for the panel storage window (RFP Scope of Works, work package 1 - pre-construction and setup: safe storage of panels)</v>
+      </c>
+      <c r="C70" s="16" t="str">
+        <f aca="false">'Build-Up'!C19</f>
+        <v>container-month</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <f aca="false">'Build-Up'!E19</f>
+        <v>1200</v>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="F70" s="18" t="n">
+        <f aca="false">2*ROUND(E51/$C$15,1)</f>
+        <v>5.6</v>
+      </c>
+      <c r="G70" s="20" t="n">
+        <f aca="false">2*ROUND(H51/$C$15,1)</f>
+        <v>4</v>
+      </c>
+      <c r="H70" s="18" t="n">
+        <f aca="false">ROUND(F70*D70,2)</f>
+        <v>6720</v>
+      </c>
+      <c r="I70" s="18" t="n">
+        <f aca="false">ROUND(G70*D70,2)</f>
+        <v>4800</v>
+      </c>
+      <c r="J70" s="19" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B71" s="17" t="str">
+        <f aca="false">'Build-Up'!B20</f>
+        <v>Workforce transport to the tank site, daily bus</v>
+      </c>
+      <c r="C71" s="16" t="str">
+        <f aca="false">'Build-Up'!C20</f>
+        <v>month</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <f aca="false">'Build-Up'!E20</f>
+        <v>4000</v>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" s="18" t="n">
+        <f aca="false">ROUND(E45/$C$15,1)</f>
+        <v>4.1</v>
+      </c>
+      <c r="G71" s="20" t="n">
+        <f aca="false">ROUND(H45/$C$15,1)</f>
+        <v>4.1</v>
+      </c>
+      <c r="H71" s="18" t="n">
+        <f aca="false">ROUND(F71*D71,2)</f>
+        <v>16400</v>
+      </c>
+      <c r="I71" s="18" t="n">
+        <f aca="false">ROUND(G71*D71,2)</f>
+        <v>16400</v>
+      </c>
+      <c r="J71" s="19" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="17" t="str">
+      <c r="B72" s="17" t="str">
         <f aca="false">'Build-Up'!B21</f>
         <v>Watchman for the tank site</v>
       </c>
-      <c r="C68" s="16" t="str">
+      <c r="C72" s="16" t="str">
         <f aca="false">'Build-Up'!C21</f>
         <v>month</v>
       </c>
-      <c r="D68" s="18" t="n">
+      <c r="D72" s="18" t="n">
         <f aca="false">'Build-Up'!E21</f>
         <v>4500</v>
       </c>
-      <c r="E68" s="18" t="n">
+      <c r="E72" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F68" s="18" t="n">
+      <c r="F72" s="18" t="n">
         <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
-      </c>
-      <c r="G68" s="20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G72" s="20" t="n">
         <f aca="false">ROUND(H45/$C$15,1)</f>
         <v>4.1</v>
       </c>
-      <c r="H68" s="18" t="n">
-        <f aca="false">ROUND(F68*D68,2)</f>
-        <v>18900</v>
-      </c>
-      <c r="I68" s="18" t="n">
-        <f aca="false">ROUND(G68*D68,2)</f>
+      <c r="H72" s="18" t="n">
+        <f aca="false">ROUND(F72*D72,2)</f>
         <v>18450</v>
       </c>
-      <c r="J68" s="19" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="16" t="s">
+      <c r="I72" s="18" t="n">
+        <f aca="false">ROUND(G72*D72,2)</f>
+        <v>18450</v>
+      </c>
+      <c r="J72" s="19" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="B69" s="17" t="str">
+      <c r="B73" s="17" t="str">
         <f aca="false">'Build-Up'!B74</f>
         <v>Boom truck (hiab) - offloading and erection support</v>
       </c>
-      <c r="C69" s="16" t="str">
+      <c r="C73" s="16" t="str">
         <f aca="false">'Build-Up'!C74</f>
         <v>day</v>
       </c>
-      <c r="D69" s="18" t="n">
+      <c r="D73" s="18" t="n">
         <f aca="false">'Build-Up'!E74</f>
         <v>1200</v>
       </c>
-      <c r="E69" s="18" t="n">
+      <c r="E73" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="F69" s="18" t="n">
+      <c r="F73" s="18" t="n">
         <f aca="false">(E48+E49)</f>
         <v>66</v>
       </c>
-      <c r="G69" s="20" t="n">
+      <c r="G73" s="20" t="n">
         <f aca="false">(H48+H49)</f>
         <v>47</v>
       </c>
-      <c r="H69" s="18" t="n">
-        <f aca="false">ROUND(F69*D69,2)</f>
+      <c r="H73" s="18" t="n">
+        <f aca="false">ROUND(F73*D73,2)</f>
         <v>79200</v>
       </c>
-      <c r="I69" s="18" t="n">
-        <f aca="false">ROUND(G69*D69,2)</f>
+      <c r="I73" s="18" t="n">
+        <f aca="false">ROUND(G73*D73,2)</f>
         <v>56400</v>
       </c>
-      <c r="J69" s="19" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="16" t="s">
+      <c r="J73" s="19" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="B70" s="17" t="str">
+      <c r="B74" s="17" t="str">
         <f aca="false">'Build-Up'!B75</f>
         <v>Telehandler / forklift</v>
       </c>
-      <c r="C70" s="16" t="str">
+      <c r="C74" s="16" t="str">
         <f aca="false">'Build-Up'!C75</f>
         <v>day</v>
       </c>
-      <c r="D70" s="18" t="n">
+      <c r="D74" s="18" t="n">
         <f aca="false">'Build-Up'!E75</f>
         <v>900</v>
       </c>
-      <c r="E70" s="18" t="n">
+      <c r="E74" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="F70" s="18" t="n">
+      <c r="F74" s="18" t="n">
         <f aca="false">(E48+E49)</f>
         <v>66</v>
       </c>
-      <c r="G70" s="20" t="n">
+      <c r="G74" s="20" t="n">
         <f aca="false">(H48+H49)</f>
         <v>47</v>
       </c>
-      <c r="H70" s="18" t="n">
-        <f aca="false">ROUND(F70*D70,2)</f>
+      <c r="H74" s="18" t="n">
+        <f aca="false">ROUND(F74*D74,2)</f>
         <v>59400</v>
       </c>
-      <c r="I70" s="18" t="n">
-        <f aca="false">ROUND(G70*D70,2)</f>
+      <c r="I74" s="18" t="n">
+        <f aca="false">ROUND(G74*D74,2)</f>
         <v>42300</v>
       </c>
-      <c r="J70" s="19" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="16" t="s">
+      <c r="J74" s="19" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="B71" s="17" t="str">
+      <c r="B75" s="17" t="str">
         <f aca="false">'Build-Up'!B77</f>
         <v>Mobile aluminium access towers, 2 No. for the access window, whole hire months</v>
       </c>
-      <c r="C71" s="16" t="str">
+      <c r="C75" s="16" t="str">
         <f aca="false">'Build-Up'!C77</f>
         <v>tower-month</v>
       </c>
-      <c r="D71" s="18" t="n">
+      <c r="D75" s="18" t="n">
         <f aca="false">'Build-Up'!E77</f>
         <v>1800</v>
       </c>
-      <c r="E71" s="18" t="n">
+      <c r="E75" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F71" s="18" t="n">
+      <c r="F75" s="18" t="n">
         <f aca="false">2*ROUNDUP(E50/$C$15,0)</f>
         <v>4</v>
       </c>
-      <c r="G71" s="20" t="n">
+      <c r="G75" s="20" t="n">
         <f aca="false">2*ROUNDUP(H50/$C$15,0)</f>
         <v>4</v>
       </c>
-      <c r="H71" s="18" t="n">
-        <f aca="false">ROUND(F71*D71,2)</f>
+      <c r="H75" s="18" t="n">
+        <f aca="false">ROUND(F75*D75,2)</f>
         <v>7200</v>
       </c>
-      <c r="I71" s="18" t="n">
-        <f aca="false">ROUND(G71*D71,2)</f>
+      <c r="I75" s="18" t="n">
+        <f aca="false">ROUND(G75*D75,2)</f>
         <v>7200</v>
       </c>
-      <c r="J71" s="19" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="16" t="s">
+      <c r="J75" s="19" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="B72" s="17" t="str">
+      <c r="B76" s="17" t="str">
         <f aca="false">'Build-Up'!B79</f>
         <v>Podium steps, 2 No. for the access window, whole hire months</v>
       </c>
-      <c r="C72" s="16" t="str">
+      <c r="C76" s="16" t="str">
         <f aca="false">'Build-Up'!C79</f>
         <v>unit-month</v>
       </c>
-      <c r="D72" s="18" t="n">
+      <c r="D76" s="18" t="n">
         <f aca="false">'Build-Up'!E79</f>
         <v>350</v>
       </c>
-      <c r="E72" s="18" t="n">
+      <c r="E76" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F72" s="18" t="n">
+      <c r="F76" s="18" t="n">
         <f aca="false">2*ROUNDUP(E50/$C$15,0)</f>
         <v>4</v>
       </c>
-      <c r="G72" s="20" t="n">
+      <c r="G76" s="20" t="n">
         <f aca="false">2*ROUNDUP(H50/$C$15,0)</f>
         <v>4</v>
       </c>
-      <c r="H72" s="18" t="n">
-        <f aca="false">ROUND(F72*D72,2)</f>
+      <c r="H76" s="18" t="n">
+        <f aca="false">ROUND(F76*D76,2)</f>
         <v>1400</v>
       </c>
-      <c r="I72" s="18" t="n">
-        <f aca="false">ROUND(G72*D72,2)</f>
+      <c r="I76" s="18" t="n">
+        <f aca="false">ROUND(G76*D76,2)</f>
         <v>1400</v>
       </c>
-      <c r="J72" s="19" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="16" t="s">
+      <c r="J76" s="19" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="B73" s="17" t="str">
+      <c r="B77" s="17" t="str">
         <f aca="false">'Build-Up'!B80</f>
         <v>Generator 100 kVA for the works, daytime running with fuel</v>
       </c>
-      <c r="C73" s="16" t="str">
+      <c r="C77" s="16" t="str">
         <f aca="false">'Build-Up'!C80</f>
         <v>month</v>
       </c>
-      <c r="D73" s="18" t="n">
+      <c r="D77" s="18" t="n">
         <f aca="false">'Build-Up'!E80</f>
         <v>11000</v>
       </c>
-      <c r="E73" s="18" t="n">
+      <c r="E77" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F73" s="18" t="n">
+      <c r="F77" s="18" t="n">
         <f aca="false">ROUND(E46/$C$15,1)</f>
-        <v>3.9</v>
-      </c>
-      <c r="G73" s="20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G77" s="20" t="n">
         <f aca="false">ROUND(H46/$C$15,1)</f>
         <v>3.8</v>
       </c>
-      <c r="H73" s="18" t="n">
-        <f aca="false">ROUND(F73*D73,2)</f>
-        <v>42900</v>
-      </c>
-      <c r="I73" s="18" t="n">
-        <f aca="false">ROUND(G73*D73,2)</f>
+      <c r="H77" s="18" t="n">
+        <f aca="false">ROUND(F77*D77,2)</f>
         <v>41800</v>
       </c>
-      <c r="J73" s="19" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="16" t="s">
+      <c r="I77" s="18" t="n">
+        <f aca="false">ROUND(G77*D77,2)</f>
+        <v>41800</v>
+      </c>
+      <c r="J77" s="19" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="B74" s="17" t="str">
+      <c r="B78" s="17" t="str">
         <f aca="false">'Build-Up'!B81</f>
         <v>Generator 30 kVA for the site office and welfare cabins, continuous running with fuel, whole period</v>
       </c>
-      <c r="C74" s="16" t="str">
+      <c r="C78" s="16" t="str">
         <f aca="false">'Build-Up'!C81</f>
         <v>month</v>
       </c>
-      <c r="D74" s="18" t="n">
+      <c r="D78" s="18" t="n">
         <f aca="false">'Build-Up'!E81</f>
         <v>6000</v>
       </c>
-      <c r="E74" s="18" t="n">
+      <c r="E78" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F74" s="18" t="n">
+      <c r="F78" s="18" t="n">
         <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
-      </c>
-      <c r="G74" s="20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G78" s="20" t="n">
         <f aca="false">ROUND(H45/$C$15,1)</f>
         <v>4.1</v>
       </c>
-      <c r="H74" s="18" t="n">
-        <f aca="false">ROUND(F74*D74,2)</f>
-        <v>25200</v>
-      </c>
-      <c r="I74" s="18" t="n">
-        <f aca="false">ROUND(G74*D74,2)</f>
+      <c r="H78" s="18" t="n">
+        <f aca="false">ROUND(F78*D78,2)</f>
         <v>24600</v>
       </c>
-      <c r="J74" s="19" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="16" t="s">
+      <c r="I78" s="18" t="n">
+        <f aca="false">ROUND(G78*D78,2)</f>
+        <v>24600</v>
+      </c>
+      <c r="J78" s="19" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="B75" s="17" t="str">
+      <c r="B79" s="17" t="str">
         <f aca="false">'Build-Up'!B82</f>
         <v>Site transport, pick-up / flatbed</v>
       </c>
-      <c r="C75" s="16" t="str">
+      <c r="C79" s="16" t="str">
         <f aca="false">'Build-Up'!C82</f>
         <v>month</v>
       </c>
-      <c r="D75" s="18" t="n">
+      <c r="D79" s="18" t="n">
         <f aca="false">'Build-Up'!E82</f>
         <v>3000</v>
       </c>
-      <c r="E75" s="18" t="n">
+      <c r="E79" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F75" s="18" t="n">
+      <c r="F79" s="18" t="n">
         <f aca="false">ROUND(E45/$C$15,1)</f>
-        <v>4.2</v>
-      </c>
-      <c r="G75" s="20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G79" s="20" t="n">
         <f aca="false">ROUND(H45/$C$15,1)</f>
         <v>4.1</v>
       </c>
-      <c r="H75" s="18" t="n">
-        <f aca="false">ROUND(F75*D75,2)</f>
-        <v>12600</v>
-      </c>
-      <c r="I75" s="18" t="n">
-        <f aca="false">ROUND(G75*D75,2)</f>
+      <c r="H79" s="18" t="n">
+        <f aca="false">ROUND(F79*D79,2)</f>
         <v>12300</v>
       </c>
-      <c r="J75" s="19" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="16" t="s">
+      <c r="I79" s="18" t="n">
+        <f aca="false">ROUND(G79*D79,2)</f>
+        <v>12300</v>
+      </c>
+      <c r="J79" s="19" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="B76" s="17" t="str">
+      <c r="B80" s="17" t="str">
         <f aca="false">'Build-Up'!B83</f>
         <v>Attendance labour for the tank supplier - 5 No. helpers for the erection window</v>
       </c>
-      <c r="C76" s="16" t="str">
+      <c r="C80" s="16" t="str">
         <f aca="false">'Build-Up'!C83</f>
         <v>man-month</v>
       </c>
-      <c r="D76" s="18" t="n">
+      <c r="D80" s="18" t="n">
         <f aca="false">'Build-Up'!E83</f>
         <v>3000</v>
       </c>
-      <c r="E76" s="18" t="n">
+      <c r="E80" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="F76" s="18" t="n">
+      <c r="F80" s="18" t="n">
         <f aca="false">5*ROUND(E47/$C$15,1)</f>
         <v>13.5</v>
       </c>
-      <c r="G76" s="20" t="n">
+      <c r="G80" s="20" t="n">
         <f aca="false">5*ROUND(H47/$C$15,1)</f>
         <v>10.5</v>
       </c>
-      <c r="H76" s="18" t="n">
-        <f aca="false">ROUND(F76*D76,2)</f>
+      <c r="H80" s="18" t="n">
+        <f aca="false">ROUND(F80*D80,2)</f>
         <v>40500</v>
       </c>
-      <c r="I76" s="18" t="n">
-        <f aca="false">ROUND(G76*D76,2)</f>
+      <c r="I80" s="18" t="n">
+        <f aca="false">ROUND(G80*D80,2)</f>
         <v>31500</v>
       </c>
-      <c r="J76" s="19" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="16" t="s">
+      <c r="J80" s="19" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="B77" s="17" t="str">
+      <c r="B81" s="17" t="str">
         <f aca="false">'Build-Up'!B84</f>
         <v>Power-tool hire</v>
       </c>
-      <c r="C77" s="16" t="str">
+      <c r="C81" s="16" t="str">
         <f aca="false">'Build-Up'!C84</f>
         <v>month</v>
       </c>
-      <c r="D77" s="18" t="n">
+      <c r="D81" s="18" t="n">
         <f aca="false">'Build-Up'!E84</f>
         <v>2500</v>
       </c>
-      <c r="E77" s="18" t="n">
+      <c r="E81" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F77" s="18" t="n">
+      <c r="F81" s="18" t="n">
         <f aca="false">ROUND(E47/$C$15,1)</f>
         <v>2.7</v>
       </c>
-      <c r="G77" s="20" t="n">
+      <c r="G81" s="20" t="n">
         <f aca="false">ROUND(H47/$C$15,1)</f>
         <v>2.1</v>
       </c>
-      <c r="H77" s="18" t="n">
-        <f aca="false">ROUND(F77*D77,2)</f>
+      <c r="H81" s="18" t="n">
+        <f aca="false">ROUND(F81*D81,2)</f>
         <v>6750</v>
       </c>
-      <c r="I77" s="18" t="n">
-        <f aca="false">ROUND(G77*D77,2)</f>
+      <c r="I81" s="18" t="n">
+        <f aca="false">ROUND(G81*D81,2)</f>
         <v>5250</v>
       </c>
-      <c r="J77" s="19" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="16" t="s">
+      <c r="J81" s="19" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="B78" s="17" t="str">
+      <c r="B82" s="17" t="str">
         <f aca="false">'Build-Up'!B87</f>
         <v>Mobile lighting towers, 2 No. for the erection window</v>
       </c>
-      <c r="C78" s="16" t="str">
+      <c r="C82" s="16" t="str">
         <f aca="false">'Build-Up'!C87</f>
         <v>unit-month</v>
       </c>
-      <c r="D78" s="18" t="n">
+      <c r="D82" s="18" t="n">
         <f aca="false">'Build-Up'!E87</f>
         <v>1200</v>
       </c>
-      <c r="E78" s="18" t="n">
+      <c r="E82" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F78" s="18" t="n">
+      <c r="F82" s="18" t="n">
         <f aca="false">2*ROUND(E47/$C$15,1)</f>
         <v>5.4</v>
       </c>
-      <c r="G78" s="20" t="n">
+      <c r="G82" s="20" t="n">
         <f aca="false">2*ROUND(H47/$C$15,1)</f>
         <v>4.2</v>
       </c>
-      <c r="H78" s="18" t="n">
-        <f aca="false">ROUND(F78*D78,2)</f>
+      <c r="H82" s="18" t="n">
+        <f aca="false">ROUND(F82*D82,2)</f>
         <v>6480</v>
       </c>
-      <c r="I78" s="18" t="n">
-        <f aca="false">ROUND(G78*D78,2)</f>
+      <c r="I82" s="18" t="n">
+        <f aca="false">ROUND(G82*D82,2)</f>
         <v>5040</v>
       </c>
-      <c r="J78" s="19" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="16" t="s">
+      <c r="J82" s="19" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="B79" s="17" t="str">
+      <c r="B83" s="17" t="str">
         <f aca="false">'Build-Up'!B100</f>
         <v>Test water - first tank fill to test level</v>
       </c>
-      <c r="C79" s="16" t="str">
+      <c r="C83" s="16" t="str">
         <f aca="false">'Build-Up'!C100</f>
         <v>m3</v>
       </c>
-      <c r="D79" s="18" t="n">
+      <c r="D83" s="18" t="n">
         <f aca="false">'Build-Up'!E100</f>
         <v>6</v>
       </c>
-      <c r="E79" s="18" t="n">
+      <c r="E83" s="18" t="n">
         <v>3774</v>
       </c>
-      <c r="F79" s="18" t="n">
+      <c r="F83" s="18" t="n">
         <f aca="false">2*3774</f>
         <v>7548</v>
       </c>
-      <c r="G79" s="20" t="n">
+      <c r="G83" s="20" t="n">
         <f aca="false">3774</f>
         <v>3774</v>
       </c>
-      <c r="H79" s="18" t="n">
-        <f aca="false">ROUND(F79*D79,2)</f>
+      <c r="H83" s="18" t="n">
+        <f aca="false">ROUND(F83*D83,2)</f>
         <v>45288</v>
       </c>
-      <c r="I79" s="18" t="n">
-        <f aca="false">ROUND(G79*D79,2)</f>
+      <c r="I83" s="18" t="n">
+        <f aca="false">ROUND(G83*D83,2)</f>
         <v>22644</v>
       </c>
-      <c r="J79" s="19" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="16" t="s">
+      <c r="J83" s="19" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="B80" s="17" t="str">
+      <c r="B84" s="17" t="str">
         <f aca="false">'Build-Up'!B101</f>
         <v>Transfer pump hire - Tank 1 to Tank 2</v>
       </c>
-      <c r="C80" s="16" t="str">
+      <c r="C84" s="16" t="str">
         <f aca="false">'Build-Up'!C101</f>
         <v>day</v>
       </c>
-      <c r="D80" s="18" t="n">
+      <c r="D84" s="18" t="n">
         <f aca="false">'Build-Up'!E101</f>
         <v>500</v>
       </c>
-      <c r="E80" s="18" t="n">
+      <c r="E84" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="F80" s="18" t="n">
+      <c r="F84" s="18" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G80" s="20" t="n">
+      <c r="G84" s="20" t="n">
         <f aca="false">7</f>
         <v>7</v>
       </c>
-      <c r="H80" s="18" t="n">
-        <f aca="false">ROUND(F80*D80,2)</f>
+      <c r="H84" s="18" t="n">
+        <f aca="false">ROUND(F84*D84,2)</f>
         <v>0</v>
       </c>
-      <c r="I80" s="18" t="n">
-        <f aca="false">ROUND(G80*D80,2)</f>
+      <c r="I84" s="18" t="n">
+        <f aca="false">ROUND(G84*D84,2)</f>
         <v>3500</v>
       </c>
-      <c r="J80" s="19" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="16" t="s">
+      <c r="J84" s="19" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="B81" s="17" t="str">
+      <c r="B85" s="17" t="str">
         <f aca="false">'Build-Up'!B102</f>
         <v>Transfer hoses and fittings hire</v>
       </c>
-      <c r="C81" s="16" t="str">
+      <c r="C85" s="16" t="str">
         <f aca="false">'Build-Up'!C102</f>
         <v>week</v>
       </c>
-      <c r="D81" s="18" t="n">
+      <c r="D85" s="18" t="n">
         <f aca="false">'Build-Up'!E102</f>
         <v>1000</v>
       </c>
-      <c r="E81" s="18" t="n">
+      <c r="E85" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F81" s="18" t="n">
+      <c r="F85" s="18" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G81" s="20" t="n">
+      <c r="G85" s="20" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="H81" s="18" t="n">
-        <f aca="false">ROUND(F81*D81,2)</f>
+      <c r="H85" s="18" t="n">
+        <f aca="false">ROUND(F85*D85,2)</f>
         <v>0</v>
       </c>
-      <c r="I81" s="18" t="n">
-        <f aca="false">ROUND(G81*D81,2)</f>
+      <c r="I85" s="18" t="n">
+        <f aca="false">ROUND(G85*D85,2)</f>
         <v>1000</v>
       </c>
-      <c r="J81" s="19" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="16" t="s">
+      <c r="J85" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="B82" s="17" t="str">
+      <c r="B86" s="17" t="str">
         <f aca="false">'Build-Up'!B103</f>
         <v>Transfer labour, 2 No. x 3 days</v>
       </c>
-      <c r="C82" s="16" t="str">
+      <c r="C86" s="16" t="str">
         <f aca="false">'Build-Up'!C103</f>
         <v>man-day</v>
       </c>
-      <c r="D82" s="18" t="n">
+      <c r="D86" s="18" t="n">
         <f aca="false">'Build-Up'!E103</f>
         <v>150</v>
       </c>
-      <c r="E82" s="18" t="n">
+      <c r="E86" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="F82" s="18" t="n">
+      <c r="F86" s="18" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G82" s="20" t="n">
+      <c r="G86" s="20" t="n">
         <f aca="false">6</f>
         <v>6</v>
       </c>
-      <c r="H82" s="18" t="n">
-        <f aca="false">ROUND(F82*D82,2)</f>
+      <c r="H86" s="18" t="n">
+        <f aca="false">ROUND(F86*D86,2)</f>
         <v>0</v>
       </c>
-      <c r="I82" s="18" t="n">
-        <f aca="false">ROUND(G82*D82,2)</f>
+      <c r="I86" s="18" t="n">
+        <f aca="false">ROUND(G86*D86,2)</f>
         <v>900</v>
       </c>
-      <c r="J82" s="19" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="16" t="s">
+      <c r="J86" s="19" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="B83" s="17" t="str">
+      <c r="B87" s="17" t="str">
         <f aca="false">'Build-Up'!B104</f>
         <v>Top-up water for losses and test level</v>
       </c>
-      <c r="C83" s="16" t="str">
+      <c r="C87" s="16" t="str">
         <f aca="false">'Build-Up'!C104</f>
         <v>m3</v>
       </c>
-      <c r="D83" s="18" t="n">
+      <c r="D87" s="18" t="n">
         <f aca="false">'Build-Up'!E104</f>
         <v>6</v>
       </c>
-      <c r="E83" s="18" t="n">
+      <c r="E87" s="18" t="n">
         <v>377</v>
       </c>
-      <c r="F83" s="18" t="n">
+      <c r="F87" s="18" t="n">
         <f aca="false">ROUND(2*3774*0.1,0)</f>
         <v>755</v>
       </c>
-      <c r="G83" s="20" t="n">
+      <c r="G87" s="20" t="n">
         <f aca="false">ROUND(3774*0.1,0)</f>
         <v>377</v>
       </c>
-      <c r="H83" s="18" t="n">
-        <f aca="false">ROUND(F83*D83,2)</f>
+      <c r="H87" s="18" t="n">
+        <f aca="false">ROUND(F87*D87,2)</f>
         <v>4530</v>
       </c>
-      <c r="I83" s="18" t="n">
-        <f aca="false">ROUND(G83*D83,2)</f>
+      <c r="I87" s="18" t="n">
+        <f aca="false">ROUND(G87*D87,2)</f>
         <v>2262</v>
       </c>
-      <c r="J83" s="19" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="16" t="s">
+      <c r="J87" s="19" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="93" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="B84" s="17" t="str">
+      <c r="B88" s="17" t="str">
         <f aca="false">'Build-Up'!B112</f>
         <v>Commissioning engineer</v>
       </c>
-      <c r="C84" s="16" t="str">
+      <c r="C88" s="16" t="str">
         <f aca="false">'Build-Up'!C112</f>
         <v>day</v>
       </c>
-      <c r="D84" s="18" t="n">
+      <c r="D88" s="18" t="n">
         <f aca="false">'Build-Up'!E112</f>
         <v>2000</v>
       </c>
-      <c r="E84" s="18" t="n">
+      <c r="E88" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="F84" s="18" t="n">
-        <f aca="false">E40+E41+2</f>
+      <c r="F88" s="18" t="n">
+        <f aca="false">E36+1</f>
         <v>8</v>
       </c>
-      <c r="G84" s="20" t="n">
+      <c r="G88" s="20" t="n">
         <f aca="false">H40+H41+2</f>
         <v>8</v>
       </c>
-      <c r="H84" s="18" t="n">
-        <f aca="false">ROUND(F84*D84,2)</f>
+      <c r="H88" s="18" t="n">
+        <f aca="false">ROUND(F88*D88,2)</f>
         <v>16000</v>
       </c>
-      <c r="I84" s="18" t="n">
-        <f aca="false">ROUND(G84*D84,2)</f>
+      <c r="I88" s="18" t="n">
+        <f aca="false">ROUND(G88*D88,2)</f>
         <v>16000</v>
       </c>
-      <c r="J84" s="19" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="16" t="s">
+      <c r="J88" s="19" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="B85" s="17" t="str">
+      <c r="B89" s="17" t="str">
         <f aca="false">'Build-Up'!B113</f>
         <v>MEP technicians - pump and network interfaces, 2 No. x 10 days (RFP Scope of Works, work package 9 - system integration)</v>
       </c>
-      <c r="C85" s="16" t="str">
+      <c r="C89" s="16" t="str">
         <f aca="false">'Build-Up'!C113</f>
         <v>man-day</v>
       </c>
-      <c r="D85" s="18" t="n">
+      <c r="D89" s="18" t="n">
         <f aca="false">'Build-Up'!E113</f>
         <v>400</v>
       </c>
-      <c r="E85" s="18" t="n">
+      <c r="E89" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="F85" s="18" t="n">
-        <f aca="false">2*(E40+E41)</f>
-        <v>12</v>
-      </c>
-      <c r="G85" s="20" t="n">
+      <c r="F89" s="18" t="n">
+        <f aca="false">2*E36</f>
+        <v>14</v>
+      </c>
+      <c r="G89" s="20" t="n">
         <f aca="false">2*(H40+H41)</f>
         <v>12</v>
       </c>
-      <c r="H85" s="18" t="n">
-        <f aca="false">ROUND(F85*D85,2)</f>
+      <c r="H89" s="18" t="n">
+        <f aca="false">ROUND(F89*D89,2)</f>
+        <v>5600</v>
+      </c>
+      <c r="I89" s="18" t="n">
+        <f aca="false">ROUND(G89*D89,2)</f>
         <v>4800</v>
       </c>
-      <c r="I85" s="18" t="n">
-        <f aca="false">ROUND(G85*D85,2)</f>
-        <v>4800</v>
-      </c>
-      <c r="J85" s="19" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="16" t="s">
+      <c r="J89" s="19" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="B86" s="17" t="str">
+      <c r="B90" s="17" t="str">
         <f aca="false">'Build-Up'!B115</f>
         <v>Integration coordination engineer - tie-ins with the Employer and Engineer</v>
       </c>
-      <c r="C86" s="16" t="str">
+      <c r="C90" s="16" t="str">
         <f aca="false">'Build-Up'!C115</f>
         <v>day</v>
       </c>
-      <c r="D86" s="18" t="n">
+      <c r="D90" s="18" t="n">
         <f aca="false">'Build-Up'!E115</f>
         <v>1000</v>
       </c>
-      <c r="E86" s="18" t="n">
+      <c r="E90" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="F86" s="18" t="n">
+      <c r="F90" s="18" t="n">
         <f aca="false">E35+1</f>
         <v>5</v>
       </c>
-      <c r="G86" s="20" t="n">
+      <c r="G90" s="20" t="n">
         <f aca="false">H35+1</f>
         <v>5</v>
       </c>
-      <c r="H86" s="18" t="n">
-        <f aca="false">ROUND(F86*D86,2)</f>
+      <c r="H90" s="18" t="n">
+        <f aca="false">ROUND(F90*D90,2)</f>
         <v>5000</v>
       </c>
-      <c r="I86" s="18" t="n">
-        <f aca="false">ROUND(G86*D86,2)</f>
+      <c r="I90" s="18" t="n">
+        <f aca="false">ROUND(G90*D90,2)</f>
         <v>5000</v>
       </c>
-      <c r="J86" s="19" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="16" t="s">
+      <c r="J90" s="19" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="B87" s="17" t="str">
+      <c r="B91" s="17" t="str">
         <f aca="false">'Build-Up'!B121</f>
         <v>Tanker and pump standby during filling and test holds</v>
       </c>
-      <c r="C87" s="16" t="str">
+      <c r="C91" s="16" t="str">
         <f aca="false">'Build-Up'!C121</f>
         <v>day</v>
       </c>
-      <c r="D87" s="18" t="n">
+      <c r="D91" s="18" t="n">
         <f aca="false">'Build-Up'!E121</f>
         <v>500</v>
       </c>
-      <c r="E87" s="18" t="n">
+      <c r="E91" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="F87" s="18" t="n">
+      <c r="F91" s="18" t="n">
         <f aca="false">8</f>
         <v>8</v>
       </c>
-      <c r="G87" s="20" t="n">
+      <c r="G91" s="20" t="n">
         <f aca="false">8</f>
         <v>8</v>
       </c>
-      <c r="H87" s="18" t="n">
-        <f aca="false">ROUND(F87*D87,2)</f>
+      <c r="H91" s="18" t="n">
+        <f aca="false">ROUND(F91*D91,2)</f>
         <v>4000</v>
       </c>
-      <c r="I87" s="18" t="n">
-        <f aca="false">ROUND(G87*D87,2)</f>
+      <c r="I91" s="18" t="n">
+        <f aca="false">ROUND(G91*D91,2)</f>
         <v>4000</v>
       </c>
-      <c r="J87" s="19" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="23"/>
-      <c r="B88" s="23" t="s">
-        <v>822</v>
-      </c>
-      <c r="C88" s="23"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="23"/>
-      <c r="F88" s="23"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="35" t="n">
-        <f aca="false">H56+H57+H58+H59+H60+H61+H62+H63+H64+H65+H66+H67+H68</f>
-        <v>265930</v>
-      </c>
-      <c r="I88" s="35" t="n">
-        <f aca="false">I56+I57+I58+I59+I60+I61+I62+I63+I64+I65+I66+I67+I68</f>
-        <v>257455</v>
-      </c>
-      <c r="J88" s="19" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="23"/>
-      <c r="B89" s="23" t="s">
-        <v>824</v>
-      </c>
-      <c r="C89" s="23"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="23"/>
-      <c r="F89" s="23"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="35" t="n">
-        <f aca="false">H69+H70+H71+H72+H73+H74+H75+H76+H77+H78</f>
-        <v>281630</v>
-      </c>
-      <c r="I89" s="35" t="n">
-        <f aca="false">I69+I70+I71+I72+I73+I74+I75+I76+I77+I78</f>
-        <v>227790</v>
-      </c>
-      <c r="J89" s="19" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="23"/>
-      <c r="B90" s="23" t="s">
-        <v>826</v>
-      </c>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="35" t="n">
-        <f aca="false">H79+H80+H81+H82+H83+H84+H85+H86+H87</f>
-        <v>79618</v>
-      </c>
-      <c r="I90" s="35" t="n">
-        <f aca="false">I79+I80+I81+I82+I83+I84+I85+I86+I87</f>
-        <v>60106</v>
-      </c>
-      <c r="J90" s="19" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="23"/>
-      <c r="B91" s="23" t="s">
-        <v>828</v>
-      </c>
-      <c r="C91" s="23"/>
-      <c r="D91" s="23"/>
-      <c r="E91" s="23"/>
-      <c r="F91" s="23"/>
-      <c r="G91" s="23"/>
-      <c r="H91" s="35" t="n">
-        <f aca="false">SUM(H56:H87)</f>
-        <v>627178</v>
-      </c>
-      <c r="I91" s="35" t="n">
-        <f aca="false">SUM(I56:I87)</f>
-        <v>545351</v>
-      </c>
       <c r="J91" s="19" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="23"/>
       <c r="B92" s="23" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C92" s="23"/>
       <c r="D92" s="23"/>
@@ -14162,20 +14220,108 @@
       <c r="F92" s="23"/>
       <c r="G92" s="23"/>
       <c r="H92" s="35" t="n">
-        <f aca="false">ROUND((Assessment!$K$19-I91+H91)*1.05,2)</f>
-        <v>7045136.24</v>
+        <f aca="false">H60+H61+H62+H63+H64+H65+H66+H67+H68+H69+H70+H71+H72</f>
+        <v>259375</v>
       </c>
       <c r="I92" s="35" t="n">
+        <f aca="false">I60+I61+I62+I63+I64+I65+I66+I67+I68+I69+I70+I71+I72</f>
+        <v>257455</v>
+      </c>
+      <c r="J92" s="19" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="23"/>
+      <c r="B93" s="23" t="s">
+        <v>834</v>
+      </c>
+      <c r="C93" s="23"/>
+      <c r="D93" s="23"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="23"/>
+      <c r="G93" s="23"/>
+      <c r="H93" s="35" t="n">
+        <f aca="false">H73+H74+H75+H76+H77+H78+H79+H80+H81+H82</f>
+        <v>279630</v>
+      </c>
+      <c r="I93" s="35" t="n">
+        <f aca="false">I73+I74+I75+I76+I77+I78+I79+I80+I81+I82</f>
+        <v>227790</v>
+      </c>
+      <c r="J93" s="19" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="23"/>
+      <c r="B94" s="23" t="s">
+        <v>836</v>
+      </c>
+      <c r="C94" s="23"/>
+      <c r="D94" s="23"/>
+      <c r="E94" s="23"/>
+      <c r="F94" s="23"/>
+      <c r="G94" s="23"/>
+      <c r="H94" s="35" t="n">
+        <f aca="false">H83+H84+H85+H86+H87+H88+H89+H90+H91</f>
+        <v>80418</v>
+      </c>
+      <c r="I94" s="35" t="n">
+        <f aca="false">I83+I84+I85+I86+I87+I88+I89+I90+I91</f>
+        <v>60106</v>
+      </c>
+      <c r="J94" s="19" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="23"/>
+      <c r="B95" s="23" t="s">
+        <v>838</v>
+      </c>
+      <c r="C95" s="23"/>
+      <c r="D95" s="23"/>
+      <c r="E95" s="23"/>
+      <c r="F95" s="23"/>
+      <c r="G95" s="23"/>
+      <c r="H95" s="35" t="n">
+        <f aca="false">SUM(H60:H91)</f>
+        <v>619423</v>
+      </c>
+      <c r="I95" s="35" t="n">
+        <f aca="false">SUM(I60:I91)</f>
+        <v>545351</v>
+      </c>
+      <c r="J95" s="19" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="23"/>
+      <c r="B96" s="23" t="s">
+        <v>840</v>
+      </c>
+      <c r="C96" s="23"/>
+      <c r="D96" s="23"/>
+      <c r="E96" s="23"/>
+      <c r="F96" s="23"/>
+      <c r="G96" s="23"/>
+      <c r="H96" s="35" t="n">
+        <f aca="false">ROUND((Assessment!$K$19-I95+H95)*1.05,2)</f>
+        <v>7036993.49</v>
+      </c>
+      <c r="I96" s="35" t="n">
         <f aca="false">Assessment!$K$21</f>
         <v>6959217.89</v>
       </c>
-      <c r="J92" s="19" t="s">
-        <v>831</v>
+      <c r="J96" s="19" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="15" t="s">
-        <v>832</v>
+        <v>842</v>
       </c>
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
@@ -14189,7 +14335,7 @@
     </row>
     <row r="101" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="11" t="s">
-        <v>833</v>
+        <v>843</v>
       </c>
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
@@ -14206,28 +14352,28 @@
         <v>561</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>834</v>
+        <v>844</v>
       </c>
       <c r="C102" s="13" t="s">
-        <v>835</v>
+        <v>845</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>836</v>
+        <v>846</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>837</v>
+        <v>847</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>838</v>
+        <v>848</v>
       </c>
       <c r="G102" s="13" t="s">
-        <v>839</v>
+        <v>849</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>841</v>
+        <v>851</v>
       </c>
       <c r="J102" s="13" t="s">
         <v>594</v>
@@ -14238,7 +14384,7 @@
         <v>1</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>842</v>
+        <v>852</v>
       </c>
       <c r="C103" s="58" t="n">
         <v>46204</v>
@@ -14252,17 +14398,17 @@
       <c r="F103" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G103" s="59" t="s">
-        <v>843</v>
+      <c r="G103" s="60" t="s">
+        <v>853</v>
       </c>
       <c r="H103" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I103" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J103" s="19" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14270,7 +14416,7 @@
         <v>2</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>846</v>
+        <v>856</v>
       </c>
       <c r="C104" s="58" t="n">
         <v>46204</v>
@@ -14284,17 +14430,17 @@
       <c r="F104" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G104" s="59" t="s">
-        <v>847</v>
+      <c r="G104" s="60" t="s">
+        <v>857</v>
       </c>
       <c r="H104" s="16" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="I104" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J104" s="19" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14302,7 +14448,7 @@
         <v>3</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>850</v>
+        <v>860</v>
       </c>
       <c r="C105" s="58" t="n">
         <v>46204</v>
@@ -14316,17 +14462,17 @@
       <c r="F105" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="59" t="s">
-        <v>851</v>
+      <c r="G105" s="60" t="s">
+        <v>861</v>
       </c>
       <c r="H105" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I105" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J105" s="19" t="s">
-        <v>852</v>
+        <v>862</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14334,7 +14480,7 @@
         <v>4</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="C106" s="58" t="n">
         <v>46224</v>
@@ -14348,17 +14494,17 @@
       <c r="F106" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G106" s="59" t="s">
+      <c r="G106" s="60" t="s">
+        <v>864</v>
+      </c>
+      <c r="H106" s="16" t="s">
         <v>854</v>
-      </c>
-      <c r="H106" s="16" t="s">
-        <v>844</v>
       </c>
       <c r="I106" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J106" s="19" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14366,7 +14512,7 @@
         <v>5</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>855</v>
+        <v>865</v>
       </c>
       <c r="C107" s="58" t="n">
         <v>46224</v>
@@ -14380,17 +14526,17 @@
       <c r="F107" s="18" t="n">
         <v>4694.84</v>
       </c>
-      <c r="G107" s="59" t="s">
-        <v>856</v>
+      <c r="G107" s="60" t="s">
+        <v>866</v>
       </c>
       <c r="H107" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I107" s="54" t="n">
         <v>24</v>
       </c>
       <c r="J107" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14398,7 +14544,7 @@
         <v>6</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="C108" s="58" t="n">
         <v>46224</v>
@@ -14412,17 +14558,17 @@
       <c r="F108" s="18" t="n">
         <v>6572.78</v>
       </c>
-      <c r="G108" s="59" t="s">
-        <v>859</v>
+      <c r="G108" s="60" t="s">
+        <v>869</v>
       </c>
       <c r="H108" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I108" s="54" t="n">
         <v>24</v>
       </c>
       <c r="J108" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14430,7 +14576,7 @@
         <v>7</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="C109" s="58" t="n">
         <v>46233</v>
@@ -14444,17 +14590,17 @@
       <c r="F109" s="18" t="n">
         <v>3756.88</v>
       </c>
-      <c r="G109" s="59" t="s">
-        <v>861</v>
+      <c r="G109" s="60" t="s">
+        <v>871</v>
       </c>
       <c r="H109" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I109" s="54" t="n">
         <v>20</v>
       </c>
       <c r="J109" s="19" t="s">
-        <v>863</v>
+        <v>873</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14462,7 +14608,7 @@
         <v>8</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="C110" s="58" t="n">
         <v>46233</v>
@@ -14476,17 +14622,17 @@
       <c r="F110" s="18" t="n">
         <v>4694.84</v>
       </c>
-      <c r="G110" s="59" t="s">
-        <v>865</v>
+      <c r="G110" s="60" t="s">
+        <v>875</v>
       </c>
       <c r="H110" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I110" s="54" t="n">
         <v>20</v>
       </c>
       <c r="J110" s="19" t="s">
-        <v>863</v>
+        <v>873</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14494,7 +14640,7 @@
         <v>9</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>866</v>
+        <v>876</v>
       </c>
       <c r="C111" s="58" t="n">
         <v>46235</v>
@@ -14508,17 +14654,17 @@
       <c r="F111" s="18" t="n">
         <v>4694.84</v>
       </c>
-      <c r="G111" s="59" t="s">
-        <v>867</v>
+      <c r="G111" s="60" t="s">
+        <v>877</v>
       </c>
       <c r="H111" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I111" s="54" t="n">
         <v>18</v>
       </c>
       <c r="J111" s="19" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14526,7 +14672,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>869</v>
+        <v>879</v>
       </c>
       <c r="C112" s="58" t="n">
         <v>46235</v>
@@ -14540,17 +14686,17 @@
       <c r="F112" s="18" t="n">
         <v>4694.84</v>
       </c>
-      <c r="G112" s="59" t="s">
-        <v>870</v>
+      <c r="G112" s="60" t="s">
+        <v>880</v>
       </c>
       <c r="H112" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I112" s="54" t="n">
         <v>32</v>
       </c>
       <c r="J112" s="19" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14558,7 +14704,7 @@
         <v>11</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>871</v>
+        <v>881</v>
       </c>
       <c r="C113" s="58" t="n">
         <v>46235</v>
@@ -14572,17 +14718,17 @@
       <c r="F113" s="18" t="n">
         <v>7512.76</v>
       </c>
-      <c r="G113" s="59" t="s">
-        <v>872</v>
+      <c r="G113" s="60" t="s">
+        <v>882</v>
       </c>
       <c r="H113" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I113" s="54" t="n">
         <v>18</v>
       </c>
       <c r="J113" s="19" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14590,7 +14736,7 @@
         <v>12</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>873</v>
+        <v>883</v>
       </c>
       <c r="C114" s="58" t="n">
         <v>46235</v>
@@ -14604,17 +14750,17 @@
       <c r="F114" s="18" t="n">
         <v>3755.87</v>
       </c>
-      <c r="G114" s="59" t="s">
-        <v>874</v>
+      <c r="G114" s="60" t="s">
+        <v>884</v>
       </c>
       <c r="H114" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I114" s="54" t="n">
         <v>18</v>
       </c>
       <c r="J114" s="19" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14622,7 +14768,7 @@
         <v>13</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>875</v>
+        <v>885</v>
       </c>
       <c r="C115" s="58" t="n">
         <v>46235</v>
@@ -14636,17 +14782,17 @@
       <c r="F115" s="18" t="n">
         <v>7512.76</v>
       </c>
-      <c r="G115" s="59" t="s">
-        <v>876</v>
+      <c r="G115" s="60" t="s">
+        <v>886</v>
       </c>
       <c r="H115" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I115" s="54" t="n">
         <v>21</v>
       </c>
       <c r="J115" s="19" t="s">
-        <v>868</v>
+        <v>878</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14654,7 +14800,7 @@
         <v>14</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="C116" s="58" t="n">
         <v>46235</v>
@@ -14668,17 +14814,17 @@
       <c r="F116" s="18" t="n">
         <v>4694.84</v>
       </c>
-      <c r="G116" s="59" t="s">
-        <v>878</v>
+      <c r="G116" s="60" t="s">
+        <v>888</v>
       </c>
       <c r="H116" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I116" s="54" t="n">
         <v>25</v>
       </c>
       <c r="J116" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14686,7 +14832,7 @@
         <v>15</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>879</v>
+        <v>889</v>
       </c>
       <c r="C117" s="58" t="n">
         <v>46235</v>
@@ -14700,17 +14846,17 @@
       <c r="F117" s="18" t="n">
         <v>4694.84</v>
       </c>
-      <c r="G117" s="59" t="s">
-        <v>880</v>
+      <c r="G117" s="60" t="s">
+        <v>890</v>
       </c>
       <c r="H117" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I117" s="54" t="n">
         <v>25</v>
       </c>
       <c r="J117" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14718,7 +14864,7 @@
         <v>16</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>881</v>
+        <v>891</v>
       </c>
       <c r="C118" s="58" t="n">
         <v>46235</v>
@@ -14732,17 +14878,17 @@
       <c r="F118" s="18" t="n">
         <v>4694.84</v>
       </c>
-      <c r="G118" s="59" t="s">
-        <v>882</v>
+      <c r="G118" s="60" t="s">
+        <v>892</v>
       </c>
       <c r="H118" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I118" s="54" t="n">
         <v>27</v>
       </c>
       <c r="J118" s="19" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14750,7 +14896,7 @@
         <v>17</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>883</v>
+        <v>893</v>
       </c>
       <c r="C119" s="58" t="n">
         <v>46235</v>
@@ -14764,17 +14910,17 @@
       <c r="F119" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G119" s="59" t="s">
-        <v>884</v>
+      <c r="G119" s="60" t="s">
+        <v>894</v>
       </c>
       <c r="H119" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I119" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J119" s="19" t="s">
-        <v>885</v>
+        <v>895</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14782,7 +14928,7 @@
         <v>18</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>886</v>
+        <v>896</v>
       </c>
       <c r="C120" s="58" t="n">
         <v>46235</v>
@@ -14796,17 +14942,17 @@
       <c r="F120" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G120" s="59" t="s">
-        <v>887</v>
+      <c r="G120" s="60" t="s">
+        <v>897</v>
       </c>
       <c r="H120" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I120" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="19" t="s">
-        <v>888</v>
+        <v>898</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14814,7 +14960,7 @@
         <v>19</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>889</v>
+        <v>899</v>
       </c>
       <c r="C121" s="58" t="n">
         <v>46235</v>
@@ -14828,17 +14974,17 @@
       <c r="F121" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G121" s="59" t="s">
-        <v>890</v>
+      <c r="G121" s="60" t="s">
+        <v>900</v>
       </c>
       <c r="H121" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I121" s="54" t="n">
         <v>23</v>
       </c>
       <c r="J121" s="19" t="s">
-        <v>891</v>
+        <v>901</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14846,7 +14992,7 @@
         <v>20</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>892</v>
+        <v>902</v>
       </c>
       <c r="C122" s="58" t="n">
         <v>46236</v>
@@ -14860,17 +15006,17 @@
       <c r="F122" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="59" t="s">
-        <v>893</v>
+      <c r="G122" s="60" t="s">
+        <v>903</v>
       </c>
       <c r="H122" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I122" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J122" s="19" t="s">
-        <v>885</v>
+        <v>895</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14878,7 +15024,7 @@
         <v>21</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>894</v>
+        <v>904</v>
       </c>
       <c r="C123" s="58" t="n">
         <v>46236</v>
@@ -14892,17 +15038,17 @@
       <c r="F123" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G123" s="59" t="s">
-        <v>895</v>
+      <c r="G123" s="60" t="s">
+        <v>905</v>
       </c>
       <c r="H123" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I123" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="19" t="s">
-        <v>888</v>
+        <v>898</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14910,7 +15056,7 @@
         <v>22</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>896</v>
+        <v>906</v>
       </c>
       <c r="C124" s="58" t="n">
         <v>46238</v>
@@ -14924,17 +15070,17 @@
       <c r="F124" s="18" t="n">
         <v>348110.34</v>
       </c>
-      <c r="G124" s="59" t="s">
-        <v>897</v>
+      <c r="G124" s="60" t="s">
+        <v>907</v>
       </c>
       <c r="H124" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I124" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="19" t="s">
-        <v>898</v>
+        <v>908</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14942,7 +15088,7 @@
         <v>23</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="C125" s="58" t="n">
         <v>46240</v>
@@ -14956,17 +15102,17 @@
       <c r="F125" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G125" s="59" t="s">
-        <v>900</v>
+      <c r="G125" s="60" t="s">
+        <v>910</v>
       </c>
       <c r="H125" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I125" s="54" t="n">
         <v>19</v>
       </c>
       <c r="J125" s="19" t="s">
-        <v>891</v>
+        <v>901</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14974,7 +15120,7 @@
         <v>24</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>901</v>
+        <v>911</v>
       </c>
       <c r="C126" s="58" t="n">
         <v>46241</v>
@@ -14988,17 +15134,17 @@
       <c r="F126" s="18" t="n">
         <v>62475</v>
       </c>
-      <c r="G126" s="59" t="s">
-        <v>902</v>
+      <c r="G126" s="60" t="s">
+        <v>912</v>
       </c>
       <c r="H126" s="16" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="I126" s="54" t="n">
         <v>35</v>
       </c>
       <c r="J126" s="19" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15006,7 +15152,7 @@
         <v>25</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>904</v>
+        <v>914</v>
       </c>
       <c r="C127" s="58" t="n">
         <v>46242</v>
@@ -15020,17 +15166,17 @@
       <c r="F127" s="18" t="n">
         <v>542616.31</v>
       </c>
-      <c r="G127" s="59" t="s">
-        <v>905</v>
+      <c r="G127" s="60" t="s">
+        <v>915</v>
       </c>
       <c r="H127" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I127" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J127" s="19" t="s">
-        <v>906</v>
+        <v>916</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15038,7 +15184,7 @@
         <v>26</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>904</v>
+        <v>914</v>
       </c>
       <c r="C128" s="58" t="n">
         <v>46242</v>
@@ -15052,17 +15198,17 @@
       <c r="F128" s="18" t="n">
         <v>542659.99</v>
       </c>
-      <c r="G128" s="59" t="s">
-        <v>907</v>
+      <c r="G128" s="60" t="s">
+        <v>917</v>
       </c>
       <c r="H128" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I128" s="54" t="n">
         <v>14</v>
       </c>
       <c r="J128" s="19" t="s">
-        <v>908</v>
+        <v>918</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15070,7 +15216,7 @@
         <v>27</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>909</v>
+        <v>919</v>
       </c>
       <c r="C129" s="58" t="n">
         <v>46244</v>
@@ -15084,17 +15230,17 @@
       <c r="F129" s="18" t="n">
         <v>2816.9</v>
       </c>
-      <c r="G129" s="59" t="s">
-        <v>910</v>
+      <c r="G129" s="60" t="s">
+        <v>920</v>
       </c>
       <c r="H129" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I129" s="54" t="n">
         <v>18</v>
       </c>
       <c r="J129" s="19" t="s">
-        <v>911</v>
+        <v>921</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15102,7 +15248,7 @@
         <v>28</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>912</v>
+        <v>922</v>
       </c>
       <c r="C130" s="58" t="n">
         <v>46246</v>
@@ -15116,17 +15262,17 @@
       <c r="F130" s="18" t="n">
         <v>26775</v>
       </c>
-      <c r="G130" s="59" t="s">
-        <v>913</v>
+      <c r="G130" s="60" t="s">
+        <v>923</v>
       </c>
       <c r="H130" s="16" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="I130" s="54" t="n">
         <v>35</v>
       </c>
       <c r="J130" s="19" t="s">
-        <v>903</v>
+        <v>913</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15134,7 +15280,7 @@
         <v>29</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="C131" s="58" t="n">
         <v>46247</v>
@@ -15148,17 +15294,17 @@
       <c r="F131" s="18" t="n">
         <v>2816.9</v>
       </c>
-      <c r="G131" s="59" t="s">
-        <v>915</v>
+      <c r="G131" s="60" t="s">
+        <v>925</v>
       </c>
       <c r="H131" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I131" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J131" s="19" t="s">
-        <v>911</v>
+        <v>921</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15166,7 +15312,7 @@
         <v>30</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>916</v>
+        <v>926</v>
       </c>
       <c r="C132" s="58" t="n">
         <v>46247</v>
@@ -15180,17 +15326,17 @@
       <c r="F132" s="18" t="n">
         <v>2816.9</v>
       </c>
-      <c r="G132" s="59" t="s">
-        <v>917</v>
+      <c r="G132" s="60" t="s">
+        <v>927</v>
       </c>
       <c r="H132" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I132" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J132" s="19" t="s">
-        <v>911</v>
+        <v>921</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15198,7 +15344,7 @@
         <v>31</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="C133" s="58" t="n">
         <v>46247</v>
@@ -15212,17 +15358,17 @@
       <c r="F133" s="18" t="n">
         <v>1877.94</v>
       </c>
-      <c r="G133" s="59" t="s">
-        <v>919</v>
+      <c r="G133" s="60" t="s">
+        <v>929</v>
       </c>
       <c r="H133" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I133" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J133" s="19" t="s">
-        <v>911</v>
+        <v>921</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15230,7 +15376,7 @@
         <v>32</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>920</v>
+        <v>930</v>
       </c>
       <c r="C134" s="58" t="n">
         <v>46247</v>
@@ -15244,17 +15390,17 @@
       <c r="F134" s="18" t="n">
         <v>3756.88</v>
       </c>
-      <c r="G134" s="59" t="s">
-        <v>921</v>
+      <c r="G134" s="60" t="s">
+        <v>931</v>
       </c>
       <c r="H134" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I134" s="54" t="n">
         <v>24</v>
       </c>
       <c r="J134" s="19" t="s">
-        <v>863</v>
+        <v>873</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15262,7 +15408,7 @@
         <v>33</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="C135" s="58" t="n">
         <v>46247</v>
@@ -15276,17 +15422,17 @@
       <c r="F135" s="18" t="n">
         <v>3756.88</v>
       </c>
-      <c r="G135" s="59" t="s">
-        <v>923</v>
+      <c r="G135" s="60" t="s">
+        <v>933</v>
       </c>
       <c r="H135" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I135" s="54" t="n">
         <v>24</v>
       </c>
       <c r="J135" s="19" t="s">
-        <v>863</v>
+        <v>873</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15294,7 +15440,7 @@
         <v>34</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>924</v>
+        <v>934</v>
       </c>
       <c r="C136" s="58" t="n">
         <v>46250</v>
@@ -15308,17 +15454,17 @@
       <c r="F136" s="18" t="n">
         <v>1877.94</v>
       </c>
-      <c r="G136" s="59" t="s">
-        <v>925</v>
+      <c r="G136" s="60" t="s">
+        <v>935</v>
       </c>
       <c r="H136" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I136" s="54" t="n">
         <v>26</v>
       </c>
       <c r="J136" s="19" t="s">
-        <v>911</v>
+        <v>921</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15326,7 +15472,7 @@
         <v>35</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>926</v>
+        <v>936</v>
       </c>
       <c r="C137" s="58" t="n">
         <v>46250</v>
@@ -15340,17 +15486,17 @@
       <c r="F137" s="18" t="n">
         <v>3756.88</v>
       </c>
-      <c r="G137" s="59" t="s">
-        <v>927</v>
+      <c r="G137" s="60" t="s">
+        <v>937</v>
       </c>
       <c r="H137" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I137" s="54" t="n">
         <v>23</v>
       </c>
       <c r="J137" s="19" t="s">
-        <v>863</v>
+        <v>873</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15358,7 +15504,7 @@
         <v>36</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="C138" s="58" t="n">
         <v>46256</v>
@@ -15372,17 +15518,17 @@
       <c r="F138" s="18" t="n">
         <v>260346.53</v>
       </c>
-      <c r="G138" s="59" t="s">
-        <v>929</v>
+      <c r="G138" s="60" t="s">
+        <v>939</v>
       </c>
       <c r="H138" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I138" s="54" t="n">
         <v>18</v>
       </c>
       <c r="J138" s="19" t="s">
-        <v>930</v>
+        <v>940</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15390,7 +15536,7 @@
         <v>37</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>931</v>
+        <v>941</v>
       </c>
       <c r="C139" s="58" t="n">
         <v>46256</v>
@@ -15404,17 +15550,17 @@
       <c r="F139" s="18" t="n">
         <v>318201.32</v>
       </c>
-      <c r="G139" s="59" t="s">
-        <v>932</v>
+      <c r="G139" s="60" t="s">
+        <v>942</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I139" s="54" t="n">
         <v>18</v>
       </c>
       <c r="J139" s="19" t="s">
-        <v>933</v>
+        <v>943</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15422,7 +15568,7 @@
         <v>38</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>886</v>
+        <v>896</v>
       </c>
       <c r="C140" s="58" t="n">
         <v>46258</v>
@@ -15436,17 +15582,17 @@
       <c r="F140" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G140" s="59" t="s">
-        <v>934</v>
+      <c r="G140" s="60" t="s">
+        <v>944</v>
       </c>
       <c r="H140" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I140" s="54" t="n">
         <v>23</v>
       </c>
       <c r="J140" s="19" t="s">
-        <v>935</v>
+        <v>945</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15454,7 +15600,7 @@
         <v>39</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>936</v>
+        <v>946</v>
       </c>
       <c r="C141" s="58" t="n">
         <v>46261</v>
@@ -15468,17 +15614,17 @@
       <c r="F141" s="18" t="n">
         <v>12086.23</v>
       </c>
-      <c r="G141" s="59" t="s">
-        <v>937</v>
+      <c r="G141" s="60" t="s">
+        <v>947</v>
       </c>
       <c r="H141" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I141" s="54" t="n">
         <v>18</v>
       </c>
       <c r="J141" s="19" t="s">
-        <v>938</v>
+        <v>948</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15486,7 +15632,7 @@
         <v>40</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>939</v>
+        <v>949</v>
       </c>
       <c r="C142" s="58" t="n">
         <v>46266</v>
@@ -15500,17 +15646,17 @@
       <c r="F142" s="18" t="n">
         <v>12086.23</v>
       </c>
-      <c r="G142" s="59" t="s">
-        <v>940</v>
+      <c r="G142" s="60" t="s">
+        <v>950</v>
       </c>
       <c r="H142" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I142" s="54" t="n">
         <v>18</v>
       </c>
       <c r="J142" s="19" t="s">
-        <v>938</v>
+        <v>948</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15518,7 +15664,7 @@
         <v>41</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>894</v>
+        <v>904</v>
       </c>
       <c r="C143" s="58" t="n">
         <v>46266</v>
@@ -15532,17 +15678,17 @@
       <c r="F143" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G143" s="59" t="s">
-        <v>941</v>
+      <c r="G143" s="60" t="s">
+        <v>951</v>
       </c>
       <c r="H143" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I143" s="54" t="n">
         <v>19</v>
       </c>
       <c r="J143" s="19" t="s">
-        <v>935</v>
+        <v>945</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15550,7 +15696,7 @@
         <v>42</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>942</v>
+        <v>952</v>
       </c>
       <c r="C144" s="58" t="n">
         <v>46270</v>
@@ -15564,17 +15710,17 @@
       <c r="F144" s="18" t="n">
         <v>56402.53</v>
       </c>
-      <c r="G144" s="59" t="s">
-        <v>943</v>
+      <c r="G144" s="60" t="s">
+        <v>953</v>
       </c>
       <c r="H144" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I144" s="54" t="n">
         <v>18</v>
       </c>
       <c r="J144" s="19" t="s">
-        <v>938</v>
+        <v>948</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15582,7 +15728,7 @@
         <v>43</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="C145" s="58" t="n">
         <v>46272</v>
@@ -15596,17 +15742,17 @@
       <c r="F145" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="G145" s="59" t="s">
-        <v>945</v>
+      <c r="G145" s="60" t="s">
+        <v>955</v>
       </c>
       <c r="H145" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I145" s="54" t="n">
         <v>18</v>
       </c>
       <c r="J145" s="19" t="s">
-        <v>946</v>
+        <v>956</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15614,7 +15760,7 @@
         <v>44</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>947</v>
+        <v>957</v>
       </c>
       <c r="C146" s="58" t="n">
         <v>46273</v>
@@ -15628,17 +15774,17 @@
       <c r="F146" s="18" t="n">
         <v>147998.19</v>
       </c>
-      <c r="G146" s="59" t="s">
-        <v>948</v>
+      <c r="G146" s="60" t="s">
+        <v>958</v>
       </c>
       <c r="H146" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I146" s="54" t="n">
         <v>14</v>
       </c>
       <c r="J146" s="19" t="s">
-        <v>908</v>
+        <v>918</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15646,7 +15792,7 @@
         <v>45</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>949</v>
+        <v>959</v>
       </c>
       <c r="C147" s="58" t="n">
         <v>46273</v>
@@ -15660,17 +15806,17 @@
       <c r="F147" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G147" s="59" t="s">
-        <v>950</v>
+      <c r="G147" s="60" t="s">
+        <v>960</v>
       </c>
       <c r="H147" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I147" s="54" t="n">
         <v>14</v>
       </c>
       <c r="J147" s="19" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15678,7 +15824,7 @@
         <v>46</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>952</v>
+        <v>962</v>
       </c>
       <c r="C148" s="58" t="n">
         <v>46274</v>
@@ -15692,17 +15838,17 @@
       <c r="F148" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G148" s="59" t="s">
-        <v>953</v>
+      <c r="G148" s="60" t="s">
+        <v>963</v>
       </c>
       <c r="H148" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I148" s="54" t="n">
         <v>12</v>
       </c>
       <c r="J148" s="19" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15710,7 +15856,7 @@
         <v>47</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>954</v>
+        <v>964</v>
       </c>
       <c r="C149" s="58" t="n">
         <v>46277</v>
@@ -15724,17 +15870,17 @@
       <c r="F149" s="18" t="n">
         <v>441252.18</v>
       </c>
-      <c r="G149" s="59" t="s">
-        <v>955</v>
+      <c r="G149" s="60" t="s">
+        <v>965</v>
       </c>
       <c r="H149" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I149" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J149" s="19" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15742,7 +15888,7 @@
         <v>48</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>896</v>
+        <v>906</v>
       </c>
       <c r="C150" s="58" t="n">
         <v>46286</v>
@@ -15756,17 +15902,17 @@
       <c r="F150" s="18" t="n">
         <v>26471.87</v>
       </c>
-      <c r="G150" s="59" t="s">
-        <v>957</v>
+      <c r="G150" s="60" t="s">
+        <v>967</v>
       </c>
       <c r="H150" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I150" s="54" t="n">
         <v>23</v>
       </c>
       <c r="J150" s="19" t="s">
-        <v>958</v>
+        <v>968</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15774,7 +15920,7 @@
         <v>49</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C151" s="58" t="n">
         <v>46292</v>
@@ -15788,17 +15934,17 @@
       <c r="F151" s="18" t="n">
         <v>149928.13</v>
       </c>
-      <c r="G151" s="59" t="s">
-        <v>960</v>
+      <c r="G151" s="60" t="s">
+        <v>970</v>
       </c>
       <c r="H151" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I151" s="54" t="n">
         <v>23</v>
       </c>
       <c r="J151" s="19" t="s">
-        <v>961</v>
+        <v>971</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15806,7 +15952,7 @@
         <v>50</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>962</v>
+        <v>972</v>
       </c>
       <c r="C152" s="58" t="n">
         <v>46299</v>
@@ -15820,17 +15966,17 @@
       <c r="F152" s="18" t="n">
         <v>295996.37</v>
       </c>
-      <c r="G152" s="59" t="s">
-        <v>963</v>
+      <c r="G152" s="60" t="s">
+        <v>973</v>
       </c>
       <c r="H152" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I152" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J152" s="19" t="s">
-        <v>908</v>
+        <v>918</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15838,7 +15984,7 @@
         <v>51</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>964</v>
+        <v>974</v>
       </c>
       <c r="C153" s="58" t="n">
         <v>46299</v>
@@ -15852,17 +15998,17 @@
       <c r="F153" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G153" s="59" t="s">
-        <v>965</v>
+      <c r="G153" s="60" t="s">
+        <v>975</v>
       </c>
       <c r="H153" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I153" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J153" s="19" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15870,7 +16016,7 @@
         <v>52</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="C154" s="58" t="n">
         <v>46300</v>
@@ -15884,17 +16030,17 @@
       <c r="F154" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G154" s="59" t="s">
-        <v>967</v>
+      <c r="G154" s="60" t="s">
+        <v>977</v>
       </c>
       <c r="H154" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I154" s="54" t="n">
         <v>13</v>
       </c>
       <c r="J154" s="19" t="s">
-        <v>951</v>
+        <v>961</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15902,7 +16048,7 @@
         <v>53</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="C155" s="58" t="n">
         <v>46301</v>
@@ -15916,17 +16062,17 @@
       <c r="F155" s="18" t="n">
         <v>701992.11</v>
       </c>
-      <c r="G155" s="59" t="s">
-        <v>969</v>
+      <c r="G155" s="60" t="s">
+        <v>979</v>
       </c>
       <c r="H155" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I155" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J155" s="19" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15934,7 +16080,7 @@
         <v>54</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="C156" s="58" t="n">
         <v>46303</v>
@@ -15948,17 +16094,17 @@
       <c r="F156" s="18" t="n">
         <v>260739.93</v>
       </c>
-      <c r="G156" s="59" t="s">
-        <v>971</v>
+      <c r="G156" s="60" t="s">
+        <v>981</v>
       </c>
       <c r="H156" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I156" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J156" s="19" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15966,7 +16112,7 @@
         <v>55</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>972</v>
+        <v>982</v>
       </c>
       <c r="C157" s="58" t="n">
         <v>46315</v>
@@ -15980,17 +16126,17 @@
       <c r="F157" s="18" t="n">
         <v>443958.8</v>
       </c>
-      <c r="G157" s="59" t="s">
-        <v>973</v>
+      <c r="G157" s="60" t="s">
+        <v>983</v>
       </c>
       <c r="H157" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I157" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J157" s="19" t="s">
-        <v>906</v>
+        <v>916</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15998,7 +16144,7 @@
         <v>56</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>974</v>
+        <v>984</v>
       </c>
       <c r="C158" s="58" t="n">
         <v>46315</v>
@@ -16012,17 +16158,17 @@
       <c r="F158" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G158" s="59" t="s">
-        <v>975</v>
+      <c r="G158" s="60" t="s">
+        <v>985</v>
       </c>
       <c r="H158" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I158" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J158" s="19" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16030,7 +16176,7 @@
         <v>57</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>954</v>
+        <v>964</v>
       </c>
       <c r="C159" s="58" t="n">
         <v>46317</v>
@@ -16044,17 +16190,17 @@
       <c r="F159" s="18" t="n">
         <v>441252.18</v>
       </c>
-      <c r="G159" s="59" t="s">
-        <v>977</v>
+      <c r="G159" s="60" t="s">
+        <v>987</v>
       </c>
       <c r="H159" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I159" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J159" s="19" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16062,7 +16208,7 @@
         <v>58</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>979</v>
+        <v>989</v>
       </c>
       <c r="C160" s="58" t="n">
         <v>46317</v>
@@ -16076,17 +16222,17 @@
       <c r="F160" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G160" s="59" t="s">
-        <v>980</v>
+      <c r="G160" s="60" t="s">
+        <v>990</v>
       </c>
       <c r="H160" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I160" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J160" s="19" t="s">
-        <v>976</v>
+        <v>986</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16094,7 +16240,7 @@
         <v>59</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="C161" s="58" t="n">
         <v>46324</v>
@@ -16108,17 +16254,17 @@
       <c r="F161" s="18" t="n">
         <v>701992.11</v>
       </c>
-      <c r="G161" s="59" t="s">
-        <v>981</v>
+      <c r="G161" s="60" t="s">
+        <v>991</v>
       </c>
       <c r="H161" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I161" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J161" s="19" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16126,7 +16272,7 @@
         <v>60</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
       <c r="C162" s="58" t="n">
         <v>46326</v>
@@ -16140,17 +16286,17 @@
       <c r="F162" s="18" t="n">
         <v>260739.93</v>
       </c>
-      <c r="G162" s="59" t="s">
-        <v>983</v>
+      <c r="G162" s="60" t="s">
+        <v>993</v>
       </c>
       <c r="H162" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I162" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J162" s="19" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16158,7 +16304,7 @@
         <v>61</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="C163" s="58" t="n">
         <v>46327</v>
@@ -16172,17 +16318,17 @@
       <c r="F163" s="18" t="n">
         <v>260739.93</v>
       </c>
-      <c r="G163" s="59" t="s">
-        <v>984</v>
+      <c r="G163" s="60" t="s">
+        <v>994</v>
       </c>
       <c r="H163" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I163" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J163" s="19" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16190,7 +16336,7 @@
         <v>62</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>985</v>
+        <v>995</v>
       </c>
       <c r="C164" s="58" t="n">
         <v>46327</v>
@@ -16204,17 +16350,17 @@
       <c r="F164" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G164" s="59" t="s">
-        <v>986</v>
+      <c r="G164" s="60" t="s">
+        <v>996</v>
       </c>
       <c r="H164" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I164" s="54" t="n">
         <v>23</v>
       </c>
       <c r="J164" s="19" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16222,7 +16368,7 @@
         <v>63</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>988</v>
+        <v>998</v>
       </c>
       <c r="C165" s="58" t="n">
         <v>46328</v>
@@ -16236,17 +16382,17 @@
       <c r="F165" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G165" s="59" t="s">
-        <v>989</v>
+      <c r="G165" s="60" t="s">
+        <v>999</v>
       </c>
       <c r="H165" s="16" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="I165" s="54" t="n">
         <v>19</v>
       </c>
       <c r="J165" s="19" t="s">
-        <v>987</v>
+        <v>997</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16254,7 +16400,7 @@
         <v>64</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="C166" s="58" t="n">
         <v>46331</v>
@@ -16268,17 +16414,17 @@
       <c r="F166" s="18" t="n">
         <v>340967.6</v>
       </c>
-      <c r="G166" s="59" t="s">
-        <v>991</v>
+      <c r="G166" s="60" t="s">
+        <v>1001</v>
       </c>
       <c r="H166" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I166" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J166" s="19" t="s">
-        <v>956</v>
+        <v>966</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16286,7 +16432,7 @@
         <v>65</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>992</v>
+        <v>1002</v>
       </c>
       <c r="C167" s="58" t="n">
         <v>46335</v>
@@ -16300,17 +16446,17 @@
       <c r="F167" s="18" t="n">
         <v>44773.92</v>
       </c>
-      <c r="G167" s="59" t="s">
-        <v>993</v>
+      <c r="G167" s="60" t="s">
+        <v>1003</v>
       </c>
       <c r="H167" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I167" s="54" t="n">
         <v>17</v>
       </c>
       <c r="J167" s="19" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16318,7 +16464,7 @@
         <v>66</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C168" s="58" t="n">
         <v>46337</v>
@@ -16332,17 +16478,17 @@
       <c r="F168" s="18" t="n">
         <v>22386.96</v>
       </c>
-      <c r="G168" s="59" t="s">
-        <v>996</v>
+      <c r="G168" s="60" t="s">
+        <v>1006</v>
       </c>
       <c r="H168" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I168" s="54" t="n">
         <v>17</v>
       </c>
       <c r="J168" s="19" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16350,7 +16496,7 @@
         <v>67</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="C169" s="58" t="n">
         <v>46338</v>
@@ -16364,17 +16510,17 @@
       <c r="F169" s="18" t="n">
         <v>156708.71</v>
       </c>
-      <c r="G169" s="59" t="s">
-        <v>998</v>
+      <c r="G169" s="60" t="s">
+        <v>1008</v>
       </c>
       <c r="H169" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I169" s="54" t="n">
         <v>15</v>
       </c>
       <c r="J169" s="19" t="s">
-        <v>994</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16382,7 +16528,7 @@
         <v>68</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>982</v>
+        <v>992</v>
       </c>
       <c r="C170" s="58" t="n">
         <v>46344</v>
@@ -16396,17 +16542,17 @@
       <c r="F170" s="18" t="n">
         <v>260739.93</v>
       </c>
-      <c r="G170" s="59" t="s">
-        <v>999</v>
+      <c r="G170" s="60" t="s">
+        <v>1009</v>
       </c>
       <c r="H170" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I170" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J170" s="19" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16414,7 +16560,7 @@
         <v>69</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="C171" s="58" t="n">
         <v>46350</v>
@@ -16428,17 +16574,17 @@
       <c r="F171" s="18" t="n">
         <v>340967.6</v>
       </c>
-      <c r="G171" s="59" t="s">
-        <v>1000</v>
+      <c r="G171" s="60" t="s">
+        <v>1010</v>
       </c>
       <c r="H171" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I171" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J171" s="19" t="s">
-        <v>978</v>
+        <v>988</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16446,7 +16592,7 @@
         <v>70</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>992</v>
+        <v>1002</v>
       </c>
       <c r="C172" s="58" t="n">
         <v>46354</v>
@@ -16460,17 +16606,17 @@
       <c r="F172" s="18" t="n">
         <v>44773.92</v>
       </c>
-      <c r="G172" s="59" t="s">
-        <v>1001</v>
+      <c r="G172" s="60" t="s">
+        <v>1011</v>
       </c>
       <c r="H172" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I172" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J172" s="19" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16478,7 +16624,7 @@
         <v>71</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>995</v>
+        <v>1005</v>
       </c>
       <c r="C173" s="58" t="n">
         <v>46356</v>
@@ -16492,17 +16638,17 @@
       <c r="F173" s="18" t="n">
         <v>22386.96</v>
       </c>
-      <c r="G173" s="59" t="s">
-        <v>1003</v>
+      <c r="G173" s="60" t="s">
+        <v>1013</v>
       </c>
       <c r="H173" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I173" s="54" t="n">
         <v>5</v>
       </c>
       <c r="J173" s="19" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16510,7 +16656,7 @@
         <v>72</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>997</v>
+        <v>1007</v>
       </c>
       <c r="C174" s="58" t="n">
         <v>46357</v>
@@ -16524,17 +16670,17 @@
       <c r="F174" s="18" t="n">
         <v>156708.71</v>
       </c>
-      <c r="G174" s="59" t="s">
-        <v>1004</v>
+      <c r="G174" s="60" t="s">
+        <v>1014</v>
       </c>
       <c r="H174" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I174" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J174" s="19" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16542,7 +16688,7 @@
         <v>73</v>
       </c>
       <c r="B175" s="17" t="s">
-        <v>1005</v>
+        <v>1015</v>
       </c>
       <c r="C175" s="58" t="n">
         <v>46359</v>
@@ -16556,17 +16702,17 @@
       <c r="F175" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G175" s="59" t="s">
-        <v>1006</v>
+      <c r="G175" s="60" t="s">
+        <v>1016</v>
       </c>
       <c r="H175" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I175" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J175" s="19" t="s">
-        <v>1007</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16574,7 +16720,7 @@
         <v>74</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>1008</v>
+        <v>1018</v>
       </c>
       <c r="C176" s="58" t="n">
         <v>46361</v>
@@ -16588,17 +16734,17 @@
       <c r="F176" s="18" t="n">
         <v>64302.97</v>
       </c>
-      <c r="G176" s="59" t="s">
-        <v>1009</v>
+      <c r="G176" s="60" t="s">
+        <v>1019</v>
       </c>
       <c r="H176" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I176" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J176" s="19" t="s">
-        <v>1007</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16606,7 +16752,7 @@
         <v>75</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="C177" s="58" t="n">
         <v>46365</v>
@@ -16620,17 +16766,17 @@
       <c r="F177" s="18" t="n">
         <v>100152.99</v>
       </c>
-      <c r="G177" s="59" t="s">
-        <v>1011</v>
+      <c r="G177" s="60" t="s">
+        <v>1021</v>
       </c>
       <c r="H177" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I177" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J177" s="19" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16638,7 +16784,7 @@
         <v>76</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>1013</v>
+        <v>1023</v>
       </c>
       <c r="C178" s="58" t="n">
         <v>46365</v>
@@ -16652,17 +16798,17 @@
       <c r="F178" s="18" t="n">
         <v>100152.99</v>
       </c>
-      <c r="G178" s="59" t="s">
-        <v>1014</v>
+      <c r="G178" s="60" t="s">
+        <v>1024</v>
       </c>
       <c r="H178" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I178" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J178" s="19" t="s">
-        <v>1012</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16670,7 +16816,7 @@
         <v>77</v>
       </c>
       <c r="B179" s="17" t="s">
-        <v>1015</v>
+        <v>1025</v>
       </c>
       <c r="C179" s="58" t="n">
         <v>46372</v>
@@ -16684,17 +16830,17 @@
       <c r="F179" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G179" s="59" t="s">
-        <v>1016</v>
+      <c r="G179" s="60" t="s">
+        <v>1026</v>
       </c>
       <c r="H179" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I179" s="54" t="n">
         <v>7</v>
       </c>
       <c r="J179" s="19" t="s">
-        <v>852</v>
+        <v>862</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16702,7 +16848,7 @@
         <v>78</v>
       </c>
       <c r="B180" s="17" t="s">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="C180" s="58" t="n">
         <v>46372</v>
@@ -16716,17 +16862,17 @@
       <c r="F180" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G180" s="59" t="s">
-        <v>1018</v>
+      <c r="G180" s="60" t="s">
+        <v>1028</v>
       </c>
       <c r="H180" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I180" s="54" t="n">
         <v>7</v>
       </c>
       <c r="J180" s="19" t="s">
-        <v>852</v>
+        <v>862</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16734,7 +16880,7 @@
         <v>79</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>1019</v>
+        <v>1029</v>
       </c>
       <c r="C181" s="58" t="n">
         <v>46373</v>
@@ -16748,17 +16894,17 @@
       <c r="F181" s="18" t="n">
         <v>50000</v>
       </c>
-      <c r="G181" s="59" t="s">
-        <v>1020</v>
+      <c r="G181" s="60" t="s">
+        <v>1030</v>
       </c>
       <c r="H181" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I181" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J181" s="19" t="s">
-        <v>1021</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16766,7 +16912,7 @@
         <v>80</v>
       </c>
       <c r="B182" s="17" t="s">
-        <v>1022</v>
+        <v>1032</v>
       </c>
       <c r="C182" s="58" t="n">
         <v>46373</v>
@@ -16780,17 +16926,17 @@
       <c r="F182" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G182" s="59" t="s">
-        <v>1023</v>
+      <c r="G182" s="60" t="s">
+        <v>1033</v>
       </c>
       <c r="H182" s="16" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="I182" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J182" s="19" t="s">
-        <v>1024</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16798,7 +16944,7 @@
         <v>81</v>
       </c>
       <c r="B183" s="17" t="s">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="C183" s="58" t="n">
         <v>46380</v>
@@ -16812,23 +16958,23 @@
       <c r="F183" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G183" s="59" t="s">
-        <v>1026</v>
+      <c r="G183" s="60" t="s">
+        <v>1036</v>
       </c>
       <c r="H183" s="16" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="I183" s="54" t="n">
         <v>0</v>
       </c>
       <c r="J183" s="19" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="23"/>
       <c r="B184" s="23" t="s">
-        <v>1027</v>
+        <v>1037</v>
       </c>
       <c r="C184" s="23"/>
       <c r="D184" s="23"/>
@@ -16841,11 +16987,11 @@
       <c r="H184" s="23"/>
       <c r="I184" s="23"/>
       <c r="J184" s="19" t="s">
-        <v>1028</v>
+        <v>1038</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="55">
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A7:J7"/>
@@ -16894,8 +17040,11 @@
     <mergeCell ref="I49:J49"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="I51:J51"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A58:J58"/>
     <mergeCell ref="A100:J100"/>
     <mergeCell ref="A101:J101"/>
   </mergeCells>
@@ -16929,34 +17078,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>1029</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>1030</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>1031</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="60" t="s">
-        <v>1032</v>
+      <c r="A4" s="61" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="61"/>
-      <c r="B5" s="61"/>
-      <c r="C5" s="62" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
+      <c r="A5" s="62"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="63" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
@@ -16978,374 +17127,374 @@
         <v>40</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>1034</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="63" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
+      <c r="A7" s="64" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="64" t="n">
+      <c r="A8" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="65" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C8" s="64" t="s">
+      <c r="B8" s="66" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C8" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="66" t="n">
+      <c r="D8" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="66" t="n">
+      <c r="E8" s="67" t="n">
         <v>816000</v>
       </c>
-      <c r="F8" s="67" t="n">
+      <c r="F8" s="68" t="n">
         <v>816000</v>
       </c>
-      <c r="G8" s="68"/>
+      <c r="G8" s="69"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="63" t="s">
+      <c r="A9" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="63"/>
-      <c r="C9" s="63"/>
-      <c r="D9" s="63"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
     </row>
     <row r="10" customFormat="false" ht="96.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="64" t="n">
+      <c r="A10" s="65" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="65" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C10" s="64" t="s">
+      <c r="B10" s="66" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C10" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="66" t="n">
+      <c r="D10" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="66" t="n">
+      <c r="E10" s="67" t="n">
         <v>102000</v>
       </c>
-      <c r="F10" s="67" t="n">
+      <c r="F10" s="68" t="n">
         <v>102000</v>
       </c>
-      <c r="G10" s="68"/>
+      <c r="G10" s="69"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="63" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B11" s="63"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
+      <c r="A11" s="64" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
     </row>
     <row r="12" customFormat="false" ht="70.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="64" t="n">
+      <c r="A12" s="65" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="65" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C12" s="64" t="s">
+      <c r="B12" s="66" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C12" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="66" t="n">
+      <c r="D12" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="66" t="n">
+      <c r="E12" s="67" t="n">
         <v>18000</v>
       </c>
-      <c r="F12" s="67" t="n">
+      <c r="F12" s="68" t="n">
         <v>18000</v>
       </c>
-      <c r="G12" s="68"/>
+      <c r="G12" s="69"/>
     </row>
     <row r="13" customFormat="false" ht="258.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="64" t="n">
+      <c r="A13" s="65" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="65" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C13" s="64" t="s">
+      <c r="B13" s="66" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C13" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="66" t="n">
+      <c r="D13" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="66" t="n">
+      <c r="E13" s="67" t="n">
         <v>31500</v>
       </c>
-      <c r="F13" s="67" t="n">
+      <c r="F13" s="68" t="n">
         <v>31500</v>
       </c>
-      <c r="G13" s="68"/>
+      <c r="G13" s="69"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
+      <c r="A14" s="64" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
     </row>
     <row r="15" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="64" t="n">
+      <c r="A15" s="65" t="n">
         <v>5</v>
       </c>
-      <c r="B15" s="65" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C15" s="64" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D15" s="66" t="n">
+      <c r="B15" s="66" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C15" s="65" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D15" s="67" t="n">
         <v>1050</v>
       </c>
-      <c r="E15" s="66" t="n">
+      <c r="E15" s="67" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="67" t="n">
+      <c r="F15" s="68" t="n">
         <v>6300</v>
       </c>
-      <c r="G15" s="68"/>
+      <c r="G15" s="69"/>
     </row>
     <row r="16" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="64" t="n">
+      <c r="A16" s="65" t="n">
         <v>6</v>
       </c>
-      <c r="B16" s="65" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C16" s="64" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D16" s="66" t="n">
+      <c r="B16" s="66" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C16" s="65" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D16" s="67" t="n">
         <v>1050</v>
       </c>
-      <c r="E16" s="66" t="n">
+      <c r="E16" s="67" t="n">
         <v>54</v>
       </c>
-      <c r="F16" s="67" t="n">
+      <c r="F16" s="68" t="n">
         <v>56700</v>
       </c>
-      <c r="G16" s="68"/>
+      <c r="G16" s="69"/>
     </row>
     <row r="17" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="64" t="n">
+      <c r="A17" s="65" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="65" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C17" s="64" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D17" s="66" t="n">
+      <c r="B17" s="66" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D17" s="67" t="n">
         <v>1050</v>
       </c>
-      <c r="E17" s="66" t="n">
+      <c r="E17" s="67" t="n">
         <v>60</v>
       </c>
-      <c r="F17" s="67" t="n">
+      <c r="F17" s="68" t="n">
         <v>63000</v>
       </c>
-      <c r="G17" s="68"/>
+      <c r="G17" s="69"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="63" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
+      <c r="A18" s="64" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
     </row>
     <row r="19" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="64" t="n">
+      <c r="A19" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="65" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C19" s="64" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D19" s="66" t="n">
+      <c r="B19" s="66" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C19" s="65" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D19" s="67" t="n">
         <v>1050</v>
       </c>
-      <c r="E19" s="66" t="n">
+      <c r="E19" s="67" t="n">
         <v>120</v>
       </c>
-      <c r="F19" s="67" t="n">
+      <c r="F19" s="68" t="n">
         <v>126000</v>
       </c>
-      <c r="G19" s="68"/>
+      <c r="G19" s="69"/>
     </row>
     <row r="20" customFormat="false" ht="186.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="64" t="n">
+      <c r="A20" s="65" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="65" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D20" s="66" t="n">
+      <c r="B20" s="66" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C20" s="65" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D20" s="67" t="n">
         <v>435.3</v>
       </c>
-      <c r="E20" s="66" t="n">
+      <c r="E20" s="67" t="n">
         <v>1920</v>
       </c>
-      <c r="F20" s="67" t="n">
+      <c r="F20" s="68" t="n">
         <v>835776</v>
       </c>
-      <c r="G20" s="68"/>
+      <c r="G20" s="69"/>
     </row>
     <row r="21" customFormat="false" ht="144" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="64" t="n">
+      <c r="A21" s="65" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="65" t="s">
+      <c r="B21" s="66" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C21" s="65" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D21" s="67" t="n">
         <v>1050</v>
       </c>
-      <c r="C21" s="64" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D21" s="66" t="n">
-        <v>1050</v>
-      </c>
-      <c r="E21" s="66" t="n">
+      <c r="E21" s="67" t="n">
         <v>108</v>
       </c>
-      <c r="F21" s="67" t="n">
+      <c r="F21" s="68" t="n">
         <v>113400</v>
       </c>
-      <c r="G21" s="68"/>
+      <c r="G21" s="69"/>
     </row>
     <row r="22" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="64" t="n">
+      <c r="A22" s="65" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="65" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C22" s="64" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D22" s="66" t="n">
+      <c r="B22" s="66" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C22" s="65" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D22" s="67" t="n">
         <v>1773.2</v>
       </c>
-      <c r="E22" s="66" t="n">
+      <c r="E22" s="67" t="n">
         <v>120</v>
       </c>
-      <c r="F22" s="67" t="n">
+      <c r="F22" s="68" t="n">
         <v>212784</v>
       </c>
-      <c r="G22" s="68"/>
+      <c r="G22" s="69"/>
     </row>
     <row r="23" customFormat="false" ht="230.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="64" t="n">
+      <c r="A23" s="65" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="65" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C23" s="64" t="s">
+      <c r="B23" s="66" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C23" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="66" t="n">
+      <c r="D23" s="67" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="66" t="n">
+      <c r="E23" s="67" t="n">
         <v>1890000</v>
       </c>
-      <c r="F23" s="67" t="n">
+      <c r="F23" s="68" t="n">
         <v>5670000</v>
       </c>
-      <c r="G23" s="68"/>
+      <c r="G23" s="69"/>
     </row>
     <row r="24" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="64" t="n">
+      <c r="A24" s="65" t="n">
         <v>13</v>
       </c>
-      <c r="B24" s="65" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C24" s="64" t="s">
+      <c r="B24" s="66" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C24" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="66" t="n">
+      <c r="D24" s="67" t="n">
         <v>3</v>
       </c>
-      <c r="E24" s="66" t="n">
+      <c r="E24" s="67" t="n">
         <v>204000</v>
       </c>
-      <c r="F24" s="67" t="n">
+      <c r="F24" s="68" t="n">
         <v>612000</v>
       </c>
-      <c r="G24" s="68"/>
+      <c r="G24" s="69"/>
     </row>
     <row r="25" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="64" t="n">
+      <c r="A25" s="65" t="n">
         <v>14</v>
       </c>
-      <c r="B25" s="65" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C25" s="64" t="s">
+      <c r="B25" s="66" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C25" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="66" t="n">
+      <c r="D25" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="66" t="n">
+      <c r="E25" s="67" t="n">
         <v>486000</v>
       </c>
-      <c r="F25" s="67" t="n">
+      <c r="F25" s="68" t="n">
         <v>486000</v>
       </c>
-      <c r="G25" s="68"/>
+      <c r="G25" s="69"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="69"/>
-      <c r="B26" s="70" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="71" t="n">
+      <c r="A26" s="70"/>
+      <c r="B26" s="71" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="72" t="n">
         <f aca="false">SUM(F8:F25)</f>
         <v>9149460</v>
       </c>
-      <c r="G26" s="69"/>
+      <c r="G26" s="70"/>
     </row>
     <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="72"/>
+      <c r="B27" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -17390,196 +17539,196 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1056</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="73" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E2" s="73" t="s">
-        <v>1058</v>
-      </c>
-      <c r="G2" s="73" t="s">
-        <v>1059</v>
-      </c>
-      <c r="I2" s="73" t="s">
-        <v>1060</v>
-      </c>
-      <c r="K2" s="73" t="s">
-        <v>1061</v>
+      <c r="C2" s="74" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E2" s="74" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G2" s="74" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I2" s="74" t="s">
+        <v>1070</v>
+      </c>
+      <c r="K2" s="74" t="s">
+        <v>1071</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="74" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C3" s="74" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E3" s="74" t="s">
-        <v>1064</v>
-      </c>
-      <c r="G3" s="74" t="s">
-        <v>1065</v>
-      </c>
-      <c r="I3" s="74" t="s">
-        <v>1066</v>
-      </c>
-      <c r="K3" s="74" t="s">
-        <v>1067</v>
+      <c r="A3" s="75" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C3" s="75" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E3" s="75" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G3" s="75" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I3" s="75" t="s">
+        <v>1076</v>
+      </c>
+      <c r="K3" s="75" t="s">
+        <v>1077</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="74" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C4" s="74" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E4" s="74" t="s">
-        <v>1070</v>
-      </c>
-      <c r="G4" s="74" t="s">
-        <v>1071</v>
-      </c>
-      <c r="I4" s="74" t="s">
-        <v>1072</v>
-      </c>
-      <c r="K4" s="74" t="s">
-        <v>1073</v>
+      <c r="A4" s="75" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C4" s="75" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E4" s="75" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G4" s="75" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I4" s="75" t="s">
+        <v>1082</v>
+      </c>
+      <c r="K4" s="75" t="s">
+        <v>1083</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="74" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C5" s="74" t="s">
-        <v>1075</v>
-      </c>
-      <c r="E5" s="74" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G5" s="74" t="s">
-        <v>1077</v>
-      </c>
-      <c r="I5" s="74" t="s">
-        <v>1078</v>
-      </c>
-      <c r="K5" s="74" t="s">
-        <v>1079</v>
+      <c r="A5" s="75" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C5" s="75" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E5" s="75" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G5" s="75" t="s">
+        <v>1087</v>
+      </c>
+      <c r="I5" s="75" t="s">
+        <v>1088</v>
+      </c>
+      <c r="K5" s="75" t="s">
+        <v>1089</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="74" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C6" s="74" t="s">
+      <c r="A6" s="75" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C6" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="74" t="s">
-        <v>1080</v>
-      </c>
-      <c r="G6" s="74" t="s">
-        <v>1081</v>
-      </c>
-      <c r="I6" s="74" t="s">
-        <v>1082</v>
-      </c>
-      <c r="K6" s="74" t="s">
-        <v>1083</v>
+      <c r="E6" s="75" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G6" s="75" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I6" s="75" t="s">
+        <v>1092</v>
+      </c>
+      <c r="K6" s="75" t="s">
+        <v>1093</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="75" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="74" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G7" s="74" t="s">
-        <v>1085</v>
-      </c>
-      <c r="I7" s="74" t="s">
-        <v>1086</v>
-      </c>
-      <c r="K7" s="74" t="s">
-        <v>1087</v>
+      <c r="E7" s="75" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G7" s="75" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I7" s="75" t="s">
+        <v>1096</v>
+      </c>
+      <c r="K7" s="75" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="74" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C8" s="74" t="s">
-        <v>1089</v>
-      </c>
-      <c r="G8" s="74" t="s">
-        <v>1090</v>
-      </c>
-      <c r="I8" s="74" t="s">
-        <v>1091</v>
-      </c>
-      <c r="K8" s="74" t="s">
-        <v>1092</v>
+      <c r="A8" s="75" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C8" s="75" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G8" s="75" t="s">
+        <v>1100</v>
+      </c>
+      <c r="I8" s="75" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K8" s="75" t="s">
+        <v>1102</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="74" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C9" s="74" t="s">
-        <v>1094</v>
-      </c>
-      <c r="G9" s="74" t="s">
-        <v>1095</v>
-      </c>
-      <c r="K9" s="74" t="s">
-        <v>1096</v>
+      <c r="A9" s="75" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C9" s="75" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G9" s="75" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K9" s="75" t="s">
+        <v>1106</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="74" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C10" s="74" t="s">
-        <v>1098</v>
-      </c>
-      <c r="G10" s="74" t="s">
-        <v>1099</v>
-      </c>
-      <c r="K10" s="74" t="s">
-        <v>1100</v>
+      <c r="A10" s="75" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C10" s="75" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G10" s="75" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K10" s="75" t="s">
+        <v>1110</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="74" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C11" s="74" t="s">
-        <v>1102</v>
-      </c>
-      <c r="G11" s="74" t="s">
-        <v>1103</v>
+      <c r="A11" s="75" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C11" s="75" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G11" s="75" t="s">
+        <v>1113</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="74" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G12" s="74" t="s">
+      <c r="A12" s="75" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G12" s="75" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="75" t="s">
-        <v>1105</v>
+      <c r="A13" s="76" t="s">
+        <v>1115</v>
       </c>
     </row>
   </sheetData>

--- a/deliverables/RFP-027/Qiddiya - TSE Irrigation Storage Tanks - Cost Assessment - Rev 02 - 30 Sep 2026.xlsx
+++ b/deliverables/RFP-027/Qiddiya - TSE Irrigation Storage Tanks - Cost Assessment - Rev 02 - 30 Sep 2026.xlsx
@@ -326,7 +326,7 @@
     <t xml:space="preserve">ASSESSED RATE BUILD-UPS</t>
   </si>
   <si>
-    <t xml:space="preserve">How to read this tab: each line is quantity x rate = amount, with the reason beside it ('Basis': what the line buys, how many, how long, the rate and where the quantity comes from). Item totals go to column J of the 'Assessment' tab; the 'Return' link on each total row goes back there. A quantity in blue is a link to the 'Programme' tab row it is calculated from - click it. Units: a 'month' is 30.4 calendar days; a 'day' is one calendar day of hire or attendance; a 'man-day' is one person for one working day; working days exclude Fridays. 'Needs confirmation' marks an assessment allowance the Contractor has not yet substantiated; 'Provisional' marks a scope or price awaiting a document. All amounts exclude VAT.</t>
+    <t xml:space="preserve">How to read this tab: each line is quantity x rate = amount, with the reason beside it ('Basis': what the line buys, how many, how long, the rate and where the quantity comes from). Item totals go to column J of the 'Assessment' tab; the 'Return' link on each total row goes back there. A quantity in blue is a link to the 'Programme' tab row it is calculated from - click it. Units: a 'month' is 30.4 calendar days; a 'day' is one calendar day of hire or attendance; a 'man-day' is one person for one working day; working days exclude Fridays. 'Needs confirmation' marks an assessed allowance the Contractor has not yet substantiated; 'Provisional' marks a scope or price awaiting a document. All amounts exclude VAT.</t>
   </si>
   <si>
     <t xml:space="preserve">Back to 'Assessment'</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">Activity QCD18TSECONIF2050, 03-Dec-2026, zero duration. An interface milestone outside the Contractor's control, taken as submitted in the submitted programme and in the assessment allowance; it, not the tank erection, fixes the earliest tie-in date</t>
+    <t xml:space="preserve">Activity QCD18TSECONIF2050, 03-Dec-2026, zero duration. An interface milestone outside the Contractor's control, taken as submitted in the SAMA Submitted Programme and in the Assessed basis; it, not the tank erection, fixes the earliest tie-in date</t>
   </si>
   <si>
     <t xml:space="preserve">P16</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">Erection window - Tank 1 base panels start to Tank 2 mechanical finish (calendar days)</t>
   </si>
   <si>
-    <t xml:space="preserve">Power tools and lighting towers are hired by the month while erection is in progress, 12-Sep to 03-Dec-2026 as submitted; the same in the submitted programme and in the assessment allowance</t>
+    <t xml:space="preserve">Power tools and lighting towers are hired by the month while erection is in progress, 12-Sep to 03-Dec-2026 as submitted; the same in the SAMA Submitted Programme and in the Assessed basis</t>
   </si>
   <si>
     <t xml:space="preserve">D6</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">Transfer hoses: not needed as submitted; 1 week allowed</t>
   </si>
   <si>
-    <t xml:space="preserve">Nil in the submitted programme and in the assessment allowance: the transfer labour is within the approved histogram helpers priced at 5.10 (Section 4, week W16)</t>
+    <t xml:space="preserve">Nil in the SAMA Submitted Programme and in the Assessed basis: the transfer labour is within the approved histogram helpers priced at 5.10 (Section 4, week W16)</t>
   </si>
   <si>
     <t xml:space="preserve">Top-up at 10 per cent of the water filled: of two fills on the SAMA Submitted Programme, of one fill in the Assessed basis (retention in Tank 1 between P18 and P19)</t>

--- a/deliverables/RFP-027/Qiddiya - TSE Irrigation Storage Tanks - Cost Assessment - Rev 02 - 30 Sep 2026.xlsx
+++ b/deliverables/RFP-027/Qiddiya - TSE Irrigation Storage Tanks - Cost Assessment - Rev 02 - 30 Sep 2026.xlsx
@@ -621,7 +621,7 @@
     <t xml:space="preserve">2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Design engineer - coordination, review of supplier calculations, method statements, ITPs</t>
+    <t xml:space="preserve">Design engineer - design coordination and review of the supplier's calculations, method statements and ITPs</t>
   </si>
   <si>
     <t xml:space="preserve">• 2 months retained: the programme shows shop drawings 07 to 25-Aug-2026 (activities QCD18TSEENG1240 and 1250) with resubmissions to 29-Sep-2026 and the pipework shop drawings still in preparation, consistent with the period assessed
@@ -673,7 +673,8 @@
     <t xml:space="preserve">• Quantity: 12.5 engineer-days for the nine documents the programme requires for this works package (QCD18TSEMOB1050 and 1080 to 1150): tank installation (with the supplier's input), pipe installation and tie-in method statements at 2 days each; HSE, CEMP, quality, execution and mobilisation plans at 1 day each, as extensions of the contract-level plans; the ITP at 1.5 days; each with one resubmission
 • Project documents for a separate site, not head-office overheads, so priced here and not in the Overhead and Profit ('Assessment' tab, row 20)
 • The dismantling method statement is inside the Item 3 quotation; submittal administration is 2.4
-• Rate: assessed allowance (Riyadh market, Sep-2026)</t>
+• Rate: assessed allowance (Riyadh market, Sep-2026)
+• Prepared 21-Jul to 15-Aug-2026, before the Item 1 site staff start on 22-Aug-2026; the design engineer at 2.1 reviews them, he does not write them</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL ITEM 2 - goes to 'Assessment' item 2, column J</t>
@@ -2011,7 +2012,7 @@
     <t xml:space="preserve">Revalidated supplier quotations; both had lapsed before the proposal was submitted</t>
   </si>
   <si>
-    <t xml:space="preserve">WT Partnership Aconex substantiation request dated 25-Aug-2026; WT Partnership follow-up clarification request (issue to be confirmed).</t>
+    <t xml:space="preserve">WT Partnership Aconex substantiation request dated 25-Aug-2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Not received</t>
@@ -8542,7 +8543,7 @@
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.354166666666667" right="0.354166666666667" top="0.5" bottom="0.433333333333333" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -21400,7 +21401,7 @@
       </c>
       <c r="B238" s="78" t="str">
         <f aca="false">'Build-Up'!B37</f>
-        <v>Design engineer - coordination, review of supplier calculations, method statements, ITPs</v>
+        <v>Design engineer - design coordination and review of the supplier's calculations, method statements and ITPs</v>
       </c>
       <c r="C238" s="86" t="s">
         <v>1236</v>

--- a/deliverables/RFP-027/Qiddiya - TSE Irrigation Storage Tanks - Cost Assessment - Rev 02 - 30 Sep 2026.xlsx
+++ b/deliverables/RFP-027/Qiddiya - TSE Irrigation Storage Tanks - Cost Assessment - Rev 02 - 30 Sep 2026.xlsx
@@ -1579,7 +1579,23 @@
 • The Daywork Schedule applies only to Engineer-instructed daywork and is not used</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Rates marked 'assessed allowance' or 'assumption' are assessed Riyadh market rates (Sep-2026): crane 50 t SAR 2,500/day; boom truck SAR 1,200/day and telehandler SAR 900/day, both with operator and fuel; scaffolding SAR 55/m2; generator 100 kVA SAR 11,000/month with fuel; general labour SAR 150/day (helpers SAR 3,900 per person-month at 26 working days); rigger SAR 250/day; site engineer SAR 12,000/month; HSE and QA/QC SAR 10,000/month; foreman SAR 8,000/month; test water SAR 15.00/m3 tankered (one 30 m3 load at the local haulage rate); site water SAR 350 per 10 m3 delivery; generator 30 kVA SAR 8,571/month continuous with fuel (hire SAR 4,000 plus diesel at SAR 1.79 a litre); local haulage SAR 450/load; HDPE PE100 pipe 355 mm outside diameter supplied and installed SAR 280/m; gate valve DN300 SAR 6,500; motorised butterfly valve DN355 as listed SAR 14,000 excluding power and control.</t>
+    <t xml:space="preserve">2. Rates marked 'assessed allowance' or 'assumption' are assessed Riyadh market rates (Sep-2026):
+• crane 50 t SAR 2,500/day
+• boom truck SAR 1,200/day and telehandler SAR 900/day, both with operator and fuel
+• scaffolding SAR 55/m2
+• generator 100 kVA SAR 11,000/month with fuel
+• general labour SAR 150/day (helpers SAR 3,900 per person-month at 26 working days)
+• rigger SAR 250/day
+• site engineer SAR 12,000/month
+• HSE and QA/QC SAR 10,000/month
+• foreman SAR 8,000/month
+• test water SAR 15.00/m3 tankered (one 30 m3 load at the local haulage rate)
+• site water SAR 350 per 10 m3 delivery
+• generator 30 kVA SAR 8,571/month continuous with fuel (hire SAR 4,000 plus diesel at SAR 1.79 a litre)
+• local haulage SAR 450/load
+• HDPE PE100 pipe 355 mm outside diameter supplied and installed SAR 280/m
+• gate valve DN300 SAR 6,500
+• motorised butterfly valve DN355 as listed SAR 14,000 excluding power and control</t>
   </si>
   <si>
     <t xml:space="preserve">3. Programme: every period on this tab comes from the Contractor's programme of 29-Sep-2026, imported as received on the 'XER WBS' tab and worked through on the 'Programme' tab
@@ -1589,7 +1605,13 @@
 • Dates after 28-Sep-2026 are forecasts</t>
   </si>
   <si>
-    <t xml:space="preserve">4. The Engineer's (KEO) email of 30-Aug-2026, relied on above: water and power are arranged by the Contractor pending the Employer's confirmation of local sources; one tank is filled and the water re-used for the second; dismantled materials are handed to the Employer at a location assumed to be local; thermal insulation is not required; the Contractor's methodology uses forklifts, cranes and pallet jacks; no CAD drawings exist beyond the marked-up schematic in the RFP.</t>
+    <t xml:space="preserve">4. The Engineer's (KEO) email of 30-Aug-2026, relied on above:
+• water and power are arranged by the Contractor pending the Employer's confirmation of local sources
+• one tank is filled and the water re-used for the second
+• dismantled materials are handed to the Employer at a location assumed to be local
+• thermal insulation is not required
+• the Contractor's methodology uses forklifts, cranes and pallet jacks
+• no CAD drawings exist beyond the marked-up schematic in the RFP</t>
   </si>
   <si>
     <t xml:space="preserve">5. The tank site is outside the D-18 site boundary
@@ -12452,7 +12474,7 @@
       <c r="F167" s="49"/>
       <c r="G167" s="49"/>
     </row>
-    <row r="168" customFormat="false" ht="63" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="223.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="49" t="s">
         <v>453</v>
       </c>
@@ -12474,7 +12496,7 @@
       <c r="F169" s="49"/>
       <c r="G169" s="49"/>
     </row>
-    <row r="170" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="49" t="s">
         <v>455</v>
       </c>
